--- a/data/running_lists.xlsx
+++ b/data/running_lists.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="104">
   <si>
     <t>Link</t>
   </si>
@@ -276,6 +276,66 @@
   </si>
   <si>
     <t>phuluuhoang16081993@gmail.com</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/groups/1167278443782686/</t>
+  </si>
+  <si>
+    <t>phuluuhoang168@gmail.com</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/groups/541837446481848/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/groups/809300869694777/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/groups/189954891343066/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/groups/vinfastgroupvietnam/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/groups/739871613010588/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/groups/SmartSolutionVinFast/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/groups/2256706854847614/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/groups/306267563852552/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/groups/vinfastvfe34clubvn/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/groups/vinfastvf5clubvnn/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/groups/vinfastvf5clubvn/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/groups/vf3vn/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/groups/vinfastvf3clubvn/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/groups/vf3clubvn369/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/groups/1330938384935849/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/groups/2824017314516168/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/groups/3506649176245689/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/groups/804472867906965/</t>
   </si>
 </sst>
 </file>
@@ -355,7 +415,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -363,7 +423,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
@@ -646,7 +705,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D75"/>
+  <dimension ref="A1:D101"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.26953125" bestFit="1" customWidth="1"/>
@@ -917,8 +976,8 @@
       <c r="C19" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D19" s="5">
-        <v>61577189999772</v>
+      <c r="D19" s="2" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
@@ -931,8 +990,8 @@
       <c r="C20" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D20" s="5">
-        <v>61577189999772</v>
+      <c r="D20" s="2" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
@@ -945,8 +1004,8 @@
       <c r="C21" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D21" s="5">
-        <v>61577189999772</v>
+      <c r="D21" s="2" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
@@ -959,8 +1018,8 @@
       <c r="C22" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D22" s="5">
-        <v>61577189999772</v>
+      <c r="D22" s="2" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
@@ -973,8 +1032,8 @@
       <c r="C23" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D23" s="5">
-        <v>61577189999772</v>
+      <c r="D23" s="2" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
@@ -987,8 +1046,8 @@
       <c r="C24" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D24" s="5">
-        <v>61577189999772</v>
+      <c r="D24" s="2" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
@@ -1001,8 +1060,8 @@
       <c r="C25" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D25" s="5">
-        <v>61577189999772</v>
+      <c r="D25" s="2" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
@@ -1015,8 +1074,8 @@
       <c r="C26" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D26" s="5">
-        <v>61577189999772</v>
+      <c r="D26" s="2" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
@@ -1029,8 +1088,8 @@
       <c r="C27" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D27" s="5">
-        <v>61577189999772</v>
+      <c r="D27" s="2" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
@@ -1043,8 +1102,8 @@
       <c r="C28" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D28" s="5">
-        <v>61577189999772</v>
+      <c r="D28" s="2" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
@@ -1057,8 +1116,8 @@
       <c r="C29" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D29" s="5">
-        <v>61577189999772</v>
+      <c r="D29" s="2" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
@@ -1071,8 +1130,8 @@
       <c r="C30" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D30" s="5">
-        <v>61577189999772</v>
+      <c r="D30" s="2" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
@@ -1085,8 +1144,8 @@
       <c r="C31" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D31" s="5">
-        <v>61577189999772</v>
+      <c r="D31" s="2" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
@@ -1099,8 +1158,8 @@
       <c r="C32" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D32" s="5">
-        <v>61577189999772</v>
+      <c r="D32" s="2" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
@@ -1113,8 +1172,8 @@
       <c r="C33" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D33" s="5">
-        <v>61577189999772</v>
+      <c r="D33" s="2" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
@@ -1127,8 +1186,8 @@
       <c r="C34" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D34" s="5">
-        <v>61577189999772</v>
+      <c r="D34" s="2" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
@@ -1141,8 +1200,8 @@
       <c r="C35" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D35" s="5">
-        <v>61577189999772</v>
+      <c r="D35" s="2" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
@@ -1155,8 +1214,8 @@
       <c r="C36" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D36" s="5">
-        <v>61577189999772</v>
+      <c r="D36" s="2" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
@@ -1169,8 +1228,8 @@
       <c r="C37" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D37" s="5">
-        <v>61577189999772</v>
+      <c r="D37" s="2" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
@@ -1183,8 +1242,8 @@
       <c r="C38" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D38" s="5">
-        <v>61577189999772</v>
+      <c r="D38" s="2" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
@@ -1620,7 +1679,382 @@
       <c r="D74" s="2"/>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C75" s="4"/>
+      <c r="A75" t="s">
+        <v>40</v>
+      </c>
+      <c r="B75" t="s">
+        <v>40</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>40</v>
+      </c>
+      <c r="B76" t="s">
+        <v>40</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>40</v>
+      </c>
+      <c r="B77" t="s">
+        <v>40</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>40</v>
+      </c>
+      <c r="B78" t="s">
+        <v>40</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>40</v>
+      </c>
+      <c r="B79" t="s">
+        <v>40</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>40</v>
+      </c>
+      <c r="B80" t="s">
+        <v>40</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>40</v>
+      </c>
+      <c r="B81" t="s">
+        <v>40</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>40</v>
+      </c>
+      <c r="B82" t="s">
+        <v>40</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>40</v>
+      </c>
+      <c r="B83" t="s">
+        <v>40</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>40</v>
+      </c>
+      <c r="B84" t="s">
+        <v>40</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>40</v>
+      </c>
+      <c r="B85" t="s">
+        <v>40</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>40</v>
+      </c>
+      <c r="B86" t="s">
+        <v>40</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>40</v>
+      </c>
+      <c r="B87" t="s">
+        <v>40</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>40</v>
+      </c>
+      <c r="B88" t="s">
+        <v>40</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>40</v>
+      </c>
+      <c r="B89" t="s">
+        <v>40</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>40</v>
+      </c>
+      <c r="B90" t="s">
+        <v>40</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>40</v>
+      </c>
+      <c r="B91" t="s">
+        <v>40</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
+        <v>40</v>
+      </c>
+      <c r="B92" t="s">
+        <v>40</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
+        <v>40</v>
+      </c>
+      <c r="B93" t="s">
+        <v>40</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
+        <v>40</v>
+      </c>
+      <c r="B94" t="s">
+        <v>40</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D94" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
+        <v>40</v>
+      </c>
+      <c r="B95" t="s">
+        <v>40</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
+        <v>40</v>
+      </c>
+      <c r="B96" t="s">
+        <v>40</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
+        <v>40</v>
+      </c>
+      <c r="B97" t="s">
+        <v>40</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
+        <v>40</v>
+      </c>
+      <c r="B98" t="s">
+        <v>40</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
+        <v>40</v>
+      </c>
+      <c r="B99" t="s">
+        <v>40</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
+        <v>40</v>
+      </c>
+      <c r="B100" t="s">
+        <v>40</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
+        <v>40</v>
+      </c>
+      <c r="B101" t="s">
+        <v>40</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>85</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1697,7 +2131,38 @@
     <hyperlink ref="C70" r:id="rId71"/>
     <hyperlink ref="C71" r:id="rId72"/>
     <hyperlink ref="C60" r:id="rId73"/>
+    <hyperlink ref="C75" r:id="rId74"/>
+    <hyperlink ref="D75" r:id="rId75"/>
+    <hyperlink ref="C76" r:id="rId76"/>
+    <hyperlink ref="C77" r:id="rId77"/>
+    <hyperlink ref="C78" r:id="rId78"/>
+    <hyperlink ref="C79" r:id="rId79"/>
+    <hyperlink ref="C80" r:id="rId80"/>
+    <hyperlink ref="C81" r:id="rId81"/>
+    <hyperlink ref="C82" r:id="rId82"/>
+    <hyperlink ref="C83" r:id="rId83"/>
+    <hyperlink ref="C84" r:id="rId84"/>
+    <hyperlink ref="C85" r:id="rId85"/>
+    <hyperlink ref="C86" r:id="rId86"/>
+    <hyperlink ref="C87" r:id="rId87"/>
+    <hyperlink ref="C88" r:id="rId88"/>
+    <hyperlink ref="C89" r:id="rId89"/>
+    <hyperlink ref="C90" r:id="rId90"/>
+    <hyperlink ref="C91" r:id="rId91"/>
+    <hyperlink ref="C92" r:id="rId92"/>
+    <hyperlink ref="C93" r:id="rId93"/>
+    <hyperlink ref="C94" r:id="rId94"/>
+    <hyperlink ref="C95" r:id="rId95"/>
+    <hyperlink ref="D76:D95" r:id="rId96" display="phuluuhoang168@gmail.com"/>
+    <hyperlink ref="C96" r:id="rId97"/>
+    <hyperlink ref="C97" r:id="rId98"/>
+    <hyperlink ref="C98" r:id="rId99"/>
+    <hyperlink ref="C99" r:id="rId100"/>
+    <hyperlink ref="C100" r:id="rId101"/>
+    <hyperlink ref="C101" r:id="rId102"/>
+    <hyperlink ref="D96:D101" r:id="rId103" display="phuluuhoang168@gmail.com"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId104"/>
 </worksheet>
 </file>
--- a/data/running_lists.xlsx
+++ b/data/running_lists.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AIML_Usecases\ai-comment-bot-main\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FB-Affiliate-Bot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11750"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11748"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="108">
   <si>
     <t>Link</t>
   </si>
@@ -336,6 +336,18 @@
   </si>
   <si>
     <t>https://www.facebook.com/groups/804472867906965/</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>ok</t>
+  </si>
+  <si>
+    <t>pending</t>
+  </si>
+  <si>
+    <t>status check</t>
   </si>
 </sst>
 </file>
@@ -386,7 +398,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -409,13 +421,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -423,6 +448,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="2" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
@@ -705,980 +734,1115 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D101"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:E100"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="50.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="50.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E1" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>40</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="6" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+        <v>104</v>
+      </c>
+      <c r="E2" s="3"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>40</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D3" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>40</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+        <v>104</v>
+      </c>
+      <c r="E4" s="3"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>40</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+        <v>104</v>
+      </c>
+      <c r="E5" s="3"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>40</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D6" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>40</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E7" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>40</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D8" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>40</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D9" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>40</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E10" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>40</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E11" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>40</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="6" t="s">
         <v>14</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E12" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>40</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+        <v>104</v>
+      </c>
+      <c r="E13" s="3"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>40</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D14" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>40</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D15" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>40</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E16" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>40</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D17" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>40</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E18" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>40</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E19" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>40</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="6" t="s">
         <v>22</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E20" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>40</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D21" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>40</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E22" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>40</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D23" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>40</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D24" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>40</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D25" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>40</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="6" t="s">
         <v>28</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E26" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>40</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+        <v>104</v>
+      </c>
+      <c r="E27" s="3"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>40</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="6" t="s">
         <v>30</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+        <v>104</v>
+      </c>
+      <c r="E28" s="3"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>40</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="6" t="s">
         <v>31</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E29" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>40</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D30" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>40</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="6" t="s">
         <v>33</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+        <v>104</v>
+      </c>
+      <c r="E31" s="3"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>40</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D32" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D32" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>40</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="6" t="s">
         <v>35</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+        <v>104</v>
+      </c>
+      <c r="E33" s="3"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>40</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="6" t="s">
         <v>36</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E34" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>40</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D35" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D35" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>40</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="C36" s="6" t="s">
         <v>37</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E36" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>40</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C37" s="2" t="s">
+      <c r="C37" s="6" t="s">
         <v>38</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E37" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>40</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D38" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D38" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>80</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="6" t="s">
         <v>46</v>
       </c>
       <c r="D39" s="2"/>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E39" s="3"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>80</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" s="6" t="s">
         <v>47</v>
       </c>
       <c r="D40" s="2"/>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E40" s="3"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>80</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C41" s="2" t="s">
+      <c r="C41" s="6" t="s">
         <v>48</v>
       </c>
       <c r="D41" s="2"/>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E41" s="3"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>80</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" s="6" t="s">
         <v>49</v>
       </c>
       <c r="D42" s="2"/>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E42" s="3"/>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>80</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C43" s="6" t="s">
         <v>50</v>
       </c>
       <c r="D43" s="2"/>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E43" s="3"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>80</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C44" s="6" t="s">
         <v>51</v>
       </c>
       <c r="D44" s="2"/>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E44" s="3"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>80</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C45" s="6" t="s">
         <v>52</v>
       </c>
       <c r="D45" s="2"/>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E45" s="3"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>80</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" s="6" t="s">
         <v>52</v>
       </c>
       <c r="D46" s="2"/>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E46" s="3"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>80</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C47" s="6" t="s">
         <v>53</v>
       </c>
       <c r="D47" s="2"/>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E47" s="3"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>80</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C48" s="6" t="s">
         <v>54</v>
       </c>
       <c r="D48" s="2"/>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E48" s="3"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>80</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="C49" s="6" t="s">
         <v>55</v>
       </c>
       <c r="D49" s="2"/>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E49" s="3"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>80</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C50" s="6" t="s">
         <v>56</v>
       </c>
       <c r="D50" s="2"/>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E50" s="3"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>80</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C51" s="2" t="s">
+      <c r="C51" s="6" t="s">
         <v>57</v>
       </c>
       <c r="D51" s="2"/>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E51" s="3"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>80</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C52" s="2" t="s">
+      <c r="C52" s="6" t="s">
         <v>58</v>
       </c>
       <c r="D52" s="2"/>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E52" s="3"/>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
         <v>80</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C53" s="2" t="s">
+      <c r="C53" s="6" t="s">
         <v>59</v>
       </c>
       <c r="D53" s="2"/>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E53" s="3"/>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>80</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C54" s="6" t="s">
         <v>60</v>
       </c>
       <c r="D54" s="2"/>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E54" s="3"/>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
         <v>80</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C55" s="6" t="s">
         <v>60</v>
       </c>
       <c r="D55" s="2"/>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E55" s="3"/>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>80</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="C56" s="6" t="s">
         <v>61</v>
       </c>
       <c r="D56" s="2"/>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E56" s="3"/>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>80</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="C57" s="6" t="s">
         <v>62</v>
       </c>
       <c r="D57" s="2"/>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E57" s="3"/>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
         <v>80</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="C58" s="6" t="s">
         <v>63</v>
       </c>
       <c r="D58" s="2"/>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E58" s="3"/>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
         <v>80</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C59" s="2" t="s">
+      <c r="C59" s="6" t="s">
         <v>64</v>
       </c>
       <c r="D59" s="2"/>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E59" s="3"/>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
         <v>80</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C60" s="2" t="s">
+      <c r="C60" s="6" t="s">
         <v>65</v>
       </c>
       <c r="D60" s="2"/>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E60" s="3"/>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
         <v>80</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C61" s="2" t="s">
+      <c r="C61" s="6" t="s">
         <v>66</v>
       </c>
       <c r="D61" s="2"/>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E61" s="3"/>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
         <v>80</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="C62" s="6" t="s">
         <v>67</v>
       </c>
       <c r="D62" s="2"/>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E62" s="3"/>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
         <v>80</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C63" s="2" t="s">
+      <c r="C63" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D63" s="2"/>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E63" s="3"/>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
         <v>80</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C64" s="2" t="s">
+      <c r="C64" s="6" t="s">
         <v>69</v>
       </c>
       <c r="D64" s="2"/>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E64" s="3"/>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
         <v>80</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C65" s="2" t="s">
+      <c r="C65" s="6" t="s">
         <v>70</v>
       </c>
       <c r="D65" s="2"/>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E65" s="3"/>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
         <v>80</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="C66" s="6" t="s">
         <v>71</v>
       </c>
       <c r="D66" s="2"/>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E66" s="3"/>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
         <v>80</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C67" s="2" t="s">
+      <c r="C67" s="6" t="s">
         <v>72</v>
       </c>
       <c r="D67" s="2"/>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E67" s="3"/>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
         <v>80</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C68" s="2" t="s">
+      <c r="C68" s="6" t="s">
         <v>73</v>
       </c>
       <c r="D68" s="2"/>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E68" s="3"/>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
         <v>80</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C69" s="2" t="s">
+      <c r="C69" s="6" t="s">
         <v>74</v>
       </c>
       <c r="D69" s="2"/>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E69" s="3"/>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
         <v>80</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="C70" s="6" t="s">
         <v>75</v>
       </c>
       <c r="D70" s="2"/>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E70" s="3"/>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
         <v>80</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C71" s="2" t="s">
+      <c r="C71" s="6" t="s">
         <v>76</v>
       </c>
       <c r="D71" s="2"/>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E71" s="3"/>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
         <v>80</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="C72" s="6" t="s">
         <v>77</v>
       </c>
       <c r="D72" s="2"/>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E72" s="3"/>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
         <v>80</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C73" s="2" t="s">
+      <c r="C73" s="6" t="s">
         <v>78</v>
       </c>
       <c r="D73" s="2"/>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E73" s="3"/>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
         <v>80</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C74" s="2" t="s">
+      <c r="C74" s="6" t="s">
         <v>79</v>
       </c>
       <c r="D74" s="2"/>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E74" s="3"/>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>40</v>
       </c>
@@ -1688,11 +1852,12 @@
       <c r="C75" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D75" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D75" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E75" s="3"/>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>40</v>
       </c>
@@ -1702,11 +1867,14 @@
       <c r="C76" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="D76" s="4" t="s">
+      <c r="D76" s="2" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E76" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>40</v>
       </c>
@@ -1716,11 +1884,12 @@
       <c r="C77" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D77" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D77" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E77" s="3"/>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>40</v>
       </c>
@@ -1730,11 +1899,14 @@
       <c r="C78" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="D78" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D78" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>40</v>
       </c>
@@ -1744,11 +1916,14 @@
       <c r="C79" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="D79" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D79" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>40</v>
       </c>
@@ -1758,11 +1933,14 @@
       <c r="C80" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="D80" s="4" t="s">
+      <c r="D80" s="2" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E80" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>40</v>
       </c>
@@ -1772,11 +1950,14 @@
       <c r="C81" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="D81" s="4" t="s">
+      <c r="D81" s="2" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E81" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>40</v>
       </c>
@@ -1786,11 +1967,12 @@
       <c r="C82" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="D82" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D82" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E82" s="3"/>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>40</v>
       </c>
@@ -1800,11 +1982,12 @@
       <c r="C83" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="D83" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="D83" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E83" s="3"/>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>40</v>
       </c>
@@ -1814,11 +1997,12 @@
       <c r="C84" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D84" s="4" t="s">
+      <c r="D84" s="2" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E84" s="3"/>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>40</v>
       </c>
@@ -1826,234 +2010,248 @@
         <v>40</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D85" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E85" s="3"/>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>40</v>
+      </c>
+      <c r="B86" t="s">
+        <v>40</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D86" s="2" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A86" t="s">
-        <v>40</v>
-      </c>
-      <c r="B86" t="s">
-        <v>40</v>
-      </c>
-      <c r="C86" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="D86" s="4" t="s">
+      <c r="E86" s="3"/>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>40</v>
+      </c>
+      <c r="B87" t="s">
+        <v>40</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>40</v>
+      </c>
+      <c r="B88" t="s">
+        <v>40</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E88" s="3"/>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>40</v>
+      </c>
+      <c r="B89" t="s">
+        <v>40</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>40</v>
+      </c>
+      <c r="B90" t="s">
+        <v>40</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D90" s="2" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A87" t="s">
-        <v>40</v>
-      </c>
-      <c r="B87" t="s">
-        <v>40</v>
-      </c>
-      <c r="C87" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="D87" s="4" t="s">
+      <c r="E90" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>40</v>
+      </c>
+      <c r="B91" t="s">
+        <v>40</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D91" s="2" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A88" t="s">
-        <v>40</v>
-      </c>
-      <c r="B88" t="s">
-        <v>40</v>
-      </c>
-      <c r="C88" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="D88" s="4" t="s">
+      <c r="E91" s="3"/>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>40</v>
+      </c>
+      <c r="B92" t="s">
+        <v>40</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D92" s="2" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A89" t="s">
-        <v>40</v>
-      </c>
-      <c r="B89" t="s">
-        <v>40</v>
-      </c>
-      <c r="C89" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D89" s="4" t="s">
+      <c r="E92" s="3"/>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>40</v>
+      </c>
+      <c r="B93" t="s">
+        <v>40</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E93" s="3"/>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>40</v>
+      </c>
+      <c r="B94" t="s">
+        <v>40</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D94" s="2" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A90" t="s">
-        <v>40</v>
-      </c>
-      <c r="B90" t="s">
-        <v>40</v>
-      </c>
-      <c r="C90" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D90" s="4" t="s">
+      <c r="E94" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A95" t="s">
+        <v>40</v>
+      </c>
+      <c r="B95" t="s">
+        <v>40</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>40</v>
+      </c>
+      <c r="B96" t="s">
+        <v>40</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E96" s="3"/>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>40</v>
+      </c>
+      <c r="B97" t="s">
+        <v>40</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E97" s="3"/>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>40</v>
+      </c>
+      <c r="B98" t="s">
+        <v>40</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E98" s="3"/>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>40</v>
+      </c>
+      <c r="B99" t="s">
+        <v>40</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E99" s="3"/>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>40</v>
+      </c>
+      <c r="B100" t="s">
+        <v>40</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D100" s="2" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A91" t="s">
-        <v>40</v>
-      </c>
-      <c r="B91" t="s">
-        <v>40</v>
-      </c>
-      <c r="C91" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D91" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A92" t="s">
-        <v>40</v>
-      </c>
-      <c r="B92" t="s">
-        <v>40</v>
-      </c>
-      <c r="C92" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D92" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A93" t="s">
-        <v>40</v>
-      </c>
-      <c r="B93" t="s">
-        <v>40</v>
-      </c>
-      <c r="C93" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D93" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A94" t="s">
-        <v>40</v>
-      </c>
-      <c r="B94" t="s">
-        <v>40</v>
-      </c>
-      <c r="C94" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="D94" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A95" t="s">
-        <v>40</v>
-      </c>
-      <c r="B95" t="s">
-        <v>40</v>
-      </c>
-      <c r="C95" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="D95" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A96" t="s">
-        <v>40</v>
-      </c>
-      <c r="B96" t="s">
-        <v>40</v>
-      </c>
-      <c r="C96" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D96" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A97" t="s">
-        <v>40</v>
-      </c>
-      <c r="B97" t="s">
-        <v>40</v>
-      </c>
-      <c r="C97" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="D97" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A98" t="s">
-        <v>40</v>
-      </c>
-      <c r="B98" t="s">
-        <v>40</v>
-      </c>
-      <c r="C98" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D98" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A99" t="s">
-        <v>40</v>
-      </c>
-      <c r="B99" t="s">
-        <v>40</v>
-      </c>
-      <c r="C99" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D99" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A100" t="s">
-        <v>40</v>
-      </c>
-      <c r="B100" t="s">
-        <v>40</v>
-      </c>
-      <c r="C100" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="D100" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A101" t="s">
-        <v>40</v>
-      </c>
-      <c r="B101" t="s">
-        <v>40</v>
-      </c>
-      <c r="C101" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="D101" s="4" t="s">
-        <v>85</v>
+      <c r="E100" s="3" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -2132,37 +2330,33 @@
     <hyperlink ref="C71" r:id="rId72"/>
     <hyperlink ref="C60" r:id="rId73"/>
     <hyperlink ref="C75" r:id="rId74"/>
-    <hyperlink ref="D75" r:id="rId75"/>
-    <hyperlink ref="C76" r:id="rId76"/>
-    <hyperlink ref="C77" r:id="rId77"/>
-    <hyperlink ref="C78" r:id="rId78"/>
-    <hyperlink ref="C79" r:id="rId79"/>
-    <hyperlink ref="C80" r:id="rId80"/>
-    <hyperlink ref="C81" r:id="rId81"/>
-    <hyperlink ref="C82" r:id="rId82"/>
-    <hyperlink ref="C83" r:id="rId83"/>
-    <hyperlink ref="C84" r:id="rId84"/>
-    <hyperlink ref="C85" r:id="rId85"/>
-    <hyperlink ref="C86" r:id="rId86"/>
-    <hyperlink ref="C87" r:id="rId87"/>
-    <hyperlink ref="C88" r:id="rId88"/>
-    <hyperlink ref="C89" r:id="rId89"/>
-    <hyperlink ref="C90" r:id="rId90"/>
-    <hyperlink ref="C91" r:id="rId91"/>
-    <hyperlink ref="C92" r:id="rId92"/>
-    <hyperlink ref="C93" r:id="rId93"/>
-    <hyperlink ref="C94" r:id="rId94"/>
-    <hyperlink ref="C95" r:id="rId95"/>
-    <hyperlink ref="D76:D95" r:id="rId96" display="phuluuhoang168@gmail.com"/>
-    <hyperlink ref="C96" r:id="rId97"/>
-    <hyperlink ref="C97" r:id="rId98"/>
-    <hyperlink ref="C98" r:id="rId99"/>
-    <hyperlink ref="C99" r:id="rId100"/>
-    <hyperlink ref="C100" r:id="rId101"/>
-    <hyperlink ref="C101" r:id="rId102"/>
-    <hyperlink ref="D96:D101" r:id="rId103" display="phuluuhoang168@gmail.com"/>
+    <hyperlink ref="C76" r:id="rId75"/>
+    <hyperlink ref="C77" r:id="rId76"/>
+    <hyperlink ref="C78" r:id="rId77"/>
+    <hyperlink ref="C79" r:id="rId78"/>
+    <hyperlink ref="C80" r:id="rId79"/>
+    <hyperlink ref="C81" r:id="rId80"/>
+    <hyperlink ref="C82" r:id="rId81"/>
+    <hyperlink ref="C83" r:id="rId82"/>
+    <hyperlink ref="C84" r:id="rId83"/>
+    <hyperlink ref="C85" r:id="rId84"/>
+    <hyperlink ref="C86" r:id="rId85"/>
+    <hyperlink ref="C87" r:id="rId86"/>
+    <hyperlink ref="C88" r:id="rId87"/>
+    <hyperlink ref="C89" r:id="rId88"/>
+    <hyperlink ref="C90" r:id="rId89"/>
+    <hyperlink ref="C91" r:id="rId90"/>
+    <hyperlink ref="C92" r:id="rId91"/>
+    <hyperlink ref="C93" r:id="rId92"/>
+    <hyperlink ref="C94" r:id="rId93"/>
+    <hyperlink ref="C95" r:id="rId94"/>
+    <hyperlink ref="C96" r:id="rId95"/>
+    <hyperlink ref="C97" r:id="rId96"/>
+    <hyperlink ref="C98" r:id="rId97"/>
+    <hyperlink ref="C99" r:id="rId98"/>
+    <hyperlink ref="C100" r:id="rId99"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId104"/>
+  <pageSetup orientation="portrait" r:id="rId100"/>
 </worksheet>
 </file>
--- a/data/running_lists.xlsx
+++ b/data/running_lists.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FB-Affiliate-Bot\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PhuLH7\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11748"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="11650" windowHeight="4780"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="129">
   <si>
     <t>Link</t>
   </si>
@@ -348,6 +348,69 @@
   </si>
   <si>
     <t>status check</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/groups/678342381651842/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/groups/muabanbsdvgp/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/groups/948011716102651/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/groups/478905373389109/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/groups/1019334229028190/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/groups/1057875204637267/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/groups/2882122705378312/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/groups/1276476517651247/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/groups/764408462178123/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/groups/2541715099413502/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/groups/vinfastvf7vn/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/groups/httpsvinfastvietnam.net.vn/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/groups/158064403823429/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/groups/3441528132775638</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/groups/vinfastvf6vietnamm/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/groups/1550860942788258/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/groups/vinfastvf6bamien/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/groups/915207669222580/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/groups/1339006012847575/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/groups/1629637303924713/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/groups/25013110648385195/</t>
   </si>
 </sst>
 </file>
@@ -734,17 +797,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E100"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E122"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="50.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="50.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -761,7 +824,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>40</v>
       </c>
@@ -776,7 +839,7 @@
       </c>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>40</v>
       </c>
@@ -793,7 +856,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>40</v>
       </c>
@@ -808,7 +871,7 @@
       </c>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>40</v>
       </c>
@@ -823,7 +886,7 @@
       </c>
       <c r="E5" s="3"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>40</v>
       </c>
@@ -840,7 +903,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>40</v>
       </c>
@@ -857,7 +920,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>40</v>
       </c>
@@ -874,7 +937,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>40</v>
       </c>
@@ -891,7 +954,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>40</v>
       </c>
@@ -908,7 +971,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>40</v>
       </c>
@@ -925,7 +988,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>40</v>
       </c>
@@ -942,7 +1005,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>40</v>
       </c>
@@ -957,7 +1020,7 @@
       </c>
       <c r="E13" s="3"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -974,7 +1037,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>40</v>
       </c>
@@ -991,7 +1054,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>40</v>
       </c>
@@ -1008,7 +1071,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -1025,7 +1088,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -1042,7 +1105,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>40</v>
       </c>
@@ -1059,7 +1122,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>40</v>
       </c>
@@ -1076,7 +1139,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>40</v>
       </c>
@@ -1093,7 +1156,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>40</v>
       </c>
@@ -1110,7 +1173,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -1127,7 +1190,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>40</v>
       </c>
@@ -1144,7 +1207,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>40</v>
       </c>
@@ -1161,7 +1224,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>40</v>
       </c>
@@ -1178,7 +1241,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>40</v>
       </c>
@@ -1193,7 +1256,7 @@
       </c>
       <c r="E27" s="3"/>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>40</v>
       </c>
@@ -1208,7 +1271,7 @@
       </c>
       <c r="E28" s="3"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -1225,7 +1288,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>40</v>
       </c>
@@ -1242,7 +1305,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>40</v>
       </c>
@@ -1257,7 +1320,7 @@
       </c>
       <c r="E31" s="3"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>40</v>
       </c>
@@ -1274,7 +1337,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>40</v>
       </c>
@@ -1289,7 +1352,7 @@
       </c>
       <c r="E33" s="3"/>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>40</v>
       </c>
@@ -1306,7 +1369,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>40</v>
       </c>
@@ -1323,7 +1386,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>40</v>
       </c>
@@ -1340,7 +1403,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>40</v>
       </c>
@@ -1357,7 +1420,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>40</v>
       </c>
@@ -1374,202 +1437,230 @@
         <v>106</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39" s="3" t="s">
-        <v>80</v>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>40</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>80</v>
+        <v>41</v>
       </c>
       <c r="C39" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E39" s="3"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E40" s="3"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E41" s="3"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>40</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E42" s="3"/>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>40</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E43" s="3"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>40</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E44" s="3"/>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>40</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E45" s="3"/>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>40</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E46" s="3"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>40</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E47" s="3"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>40</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E48" s="3"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>40</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E49" s="3"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>40</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E50" s="3"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>40</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E51" s="3"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>40</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E52" s="3"/>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A53" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C53" s="6" t="s">
         <v>46</v>
-      </c>
-      <c r="D39" s="2"/>
-      <c r="E39" s="3"/>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="D40" s="2"/>
-      <c r="E40" s="3"/>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="D41" s="2"/>
-      <c r="E41" s="3"/>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D42" s="2"/>
-      <c r="E42" s="3"/>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="D43" s="2"/>
-      <c r="E43" s="3"/>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A44" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D44" s="2"/>
-      <c r="E44" s="3"/>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A45" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C45" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D45" s="2"/>
-      <c r="E45" s="3"/>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A46" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D46" s="2"/>
-      <c r="E46" s="3"/>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A47" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C47" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="D47" s="2"/>
-      <c r="E47" s="3"/>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D48" s="2"/>
-      <c r="E48" s="3"/>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A49" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="D49" s="2"/>
-      <c r="E49" s="3"/>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A50" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C50" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="D50" s="2"/>
-      <c r="E50" s="3"/>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A51" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C51" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="D51" s="2"/>
-      <c r="E51" s="3"/>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A52" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C52" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="D52" s="2"/>
-      <c r="E52" s="3"/>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A53" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C53" s="6" t="s">
-        <v>59</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" s="3"/>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" s="3" t="s">
         <v>80</v>
       </c>
@@ -1577,12 +1668,12 @@
         <v>80</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" s="3"/>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" s="3" t="s">
         <v>80</v>
       </c>
@@ -1590,12 +1681,12 @@
         <v>80</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" s="3"/>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" s="3" t="s">
         <v>80</v>
       </c>
@@ -1603,12 +1694,12 @@
         <v>80</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" s="3"/>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" s="3" t="s">
         <v>80</v>
       </c>
@@ -1616,12 +1707,12 @@
         <v>80</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" s="3"/>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" s="3" t="s">
         <v>80</v>
       </c>
@@ -1629,12 +1720,12 @@
         <v>80</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="3"/>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" s="3" t="s">
         <v>80</v>
       </c>
@@ -1642,12 +1733,12 @@
         <v>80</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="D59" s="2"/>
       <c r="E59" s="3"/>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" s="3" t="s">
         <v>80</v>
       </c>
@@ -1655,12 +1746,12 @@
         <v>80</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" s="3"/>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" s="3" t="s">
         <v>80</v>
       </c>
@@ -1668,12 +1759,12 @@
         <v>80</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" s="3"/>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" s="3" t="s">
         <v>80</v>
       </c>
@@ -1681,12 +1772,12 @@
         <v>80</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" s="3"/>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" s="3" t="s">
         <v>80</v>
       </c>
@@ -1694,12 +1785,12 @@
         <v>80</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" s="3"/>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" s="3" t="s">
         <v>80</v>
       </c>
@@ -1707,12 +1798,12 @@
         <v>80</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" s="3"/>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" s="3" t="s">
         <v>80</v>
       </c>
@@ -1720,12 +1811,12 @@
         <v>80</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" s="3"/>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" s="3" t="s">
         <v>80</v>
       </c>
@@ -1733,12 +1824,12 @@
         <v>80</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" s="3"/>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" s="3" t="s">
         <v>80</v>
       </c>
@@ -1746,12 +1837,12 @@
         <v>80</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="D67" s="2"/>
       <c r="E67" s="3"/>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" s="3" t="s">
         <v>80</v>
       </c>
@@ -1759,12 +1850,12 @@
         <v>80</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="D68" s="2"/>
       <c r="E68" s="3"/>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" s="3" t="s">
         <v>80</v>
       </c>
@@ -1772,12 +1863,12 @@
         <v>80</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="D69" s="2"/>
       <c r="E69" s="3"/>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" s="3" t="s">
         <v>80</v>
       </c>
@@ -1785,12 +1876,12 @@
         <v>80</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="D70" s="2"/>
       <c r="E70" s="3"/>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" s="3" t="s">
         <v>80</v>
       </c>
@@ -1798,298 +1889,256 @@
         <v>80</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" s="3"/>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" s="3" t="s">
         <v>80</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="D72" s="2"/>
       <c r="E72" s="3"/>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" s="3" t="s">
         <v>80</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="D73" s="2"/>
       <c r="E73" s="3"/>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" s="3" t="s">
         <v>80</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" s="3"/>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
-        <v>40</v>
-      </c>
-      <c r="B75" t="s">
-        <v>40</v>
-      </c>
-      <c r="C75" s="4" t="s">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A75" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D75" s="2"/>
+      <c r="E75" s="3"/>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A76" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D76" s="2"/>
+      <c r="E76" s="3"/>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A77" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C77" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D77" s="2"/>
+      <c r="E77" s="3"/>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A78" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D78" s="2"/>
+      <c r="E78" s="3"/>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A79" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="D79" s="2"/>
+      <c r="E79" s="3"/>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A80" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D80" s="2"/>
+      <c r="E80" s="3"/>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A81" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D81" s="2"/>
+      <c r="E81" s="3"/>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A82" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D82" s="2"/>
+      <c r="E82" s="3"/>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A83" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D83" s="2"/>
+      <c r="E83" s="3"/>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A84" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D84" s="2"/>
+      <c r="E84" s="3"/>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A85" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C85" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D85" s="2"/>
+      <c r="E85" s="3"/>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A86" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="D86" s="2"/>
+      <c r="E86" s="3"/>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A87" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="D87" s="2"/>
+      <c r="E87" s="3"/>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A88" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C88" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="D88" s="2"/>
+      <c r="E88" s="3"/>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>40</v>
+      </c>
+      <c r="B89" t="s">
+        <v>40</v>
+      </c>
+      <c r="C89" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D75" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="E75" s="3"/>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
-        <v>40</v>
-      </c>
-      <c r="B76" t="s">
-        <v>40</v>
-      </c>
-      <c r="C76" s="4" t="s">
+      <c r="D89" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E89" s="3"/>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>40</v>
+      </c>
+      <c r="B90" t="s">
+        <v>40</v>
+      </c>
+      <c r="C90" s="4" t="s">
         <v>86</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E76" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
-        <v>40</v>
-      </c>
-      <c r="B77" t="s">
-        <v>40</v>
-      </c>
-      <c r="C77" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E77" s="3"/>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
-        <v>40</v>
-      </c>
-      <c r="B78" t="s">
-        <v>40</v>
-      </c>
-      <c r="C78" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="D78" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="E78" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
-        <v>40</v>
-      </c>
-      <c r="B79" t="s">
-        <v>40</v>
-      </c>
-      <c r="C79" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D79" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="E79" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
-        <v>40</v>
-      </c>
-      <c r="B80" t="s">
-        <v>40</v>
-      </c>
-      <c r="C80" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E80" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
-        <v>40</v>
-      </c>
-      <c r="B81" t="s">
-        <v>40</v>
-      </c>
-      <c r="C81" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
-        <v>40</v>
-      </c>
-      <c r="B82" t="s">
-        <v>40</v>
-      </c>
-      <c r="C82" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E82" s="3"/>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
-        <v>40</v>
-      </c>
-      <c r="B83" t="s">
-        <v>40</v>
-      </c>
-      <c r="C83" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E83" s="3"/>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
-        <v>40</v>
-      </c>
-      <c r="B84" t="s">
-        <v>40</v>
-      </c>
-      <c r="C84" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E84" s="3"/>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
-        <v>40</v>
-      </c>
-      <c r="B85" t="s">
-        <v>40</v>
-      </c>
-      <c r="C85" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E85" s="3"/>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
-        <v>40</v>
-      </c>
-      <c r="B86" t="s">
-        <v>40</v>
-      </c>
-      <c r="C86" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E86" s="3"/>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
-        <v>40</v>
-      </c>
-      <c r="B87" t="s">
-        <v>40</v>
-      </c>
-      <c r="C87" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="D87" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="E87" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
-        <v>40</v>
-      </c>
-      <c r="B88" t="s">
-        <v>40</v>
-      </c>
-      <c r="C88" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E88" s="3"/>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
-        <v>40</v>
-      </c>
-      <c r="B89" t="s">
-        <v>40</v>
-      </c>
-      <c r="C89" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D89" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
-        <v>40</v>
-      </c>
-      <c r="B90" t="s">
-        <v>40</v>
-      </c>
-      <c r="C90" s="4" t="s">
-        <v>27</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>85</v>
@@ -2098,7 +2147,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>40</v>
       </c>
@@ -2106,14 +2155,14 @@
         <v>40</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="E91" s="3"/>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>40</v>
       </c>
@@ -2121,14 +2170,16 @@
         <v>40</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E92" s="3"/>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>40</v>
       </c>
@@ -2136,14 +2187,16 @@
         <v>40</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E93" s="3"/>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+        <v>89</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>40</v>
       </c>
@@ -2151,7 +2204,7 @@
         <v>40</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>85</v>
@@ -2160,7 +2213,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>40</v>
       </c>
@@ -2168,16 +2221,16 @@
         <v>40</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D95" s="3" t="s">
-        <v>106</v>
+        <v>91</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>40</v>
       </c>
@@ -2185,14 +2238,14 @@
         <v>40</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>104</v>
       </c>
       <c r="E96" s="3"/>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>40</v>
       </c>
@@ -2200,14 +2253,14 @@
         <v>40</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>6</v>
+        <v>93</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>104</v>
       </c>
       <c r="E97" s="3"/>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>40</v>
       </c>
@@ -2215,14 +2268,14 @@
         <v>40</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>11</v>
+        <v>94</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="E98" s="3"/>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>40</v>
       </c>
@@ -2230,14 +2283,14 @@
         <v>40</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>104</v>
       </c>
       <c r="E99" s="3"/>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>40</v>
       </c>
@@ -2245,13 +2298,345 @@
         <v>40</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E100" s="3" t="s">
+      <c r="E100" s="3"/>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
+        <v>40</v>
+      </c>
+      <c r="B101" t="s">
+        <v>40</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
+        <v>40</v>
+      </c>
+      <c r="B102" t="s">
+        <v>40</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E102" s="3"/>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
+        <v>40</v>
+      </c>
+      <c r="B103" t="s">
+        <v>40</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
+        <v>40</v>
+      </c>
+      <c r="B104" t="s">
+        <v>40</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E104" s="3" t="s">
         <v>105</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A105" t="s">
+        <v>40</v>
+      </c>
+      <c r="B105" t="s">
+        <v>40</v>
+      </c>
+      <c r="C105" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E105" s="3"/>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A106" t="s">
+        <v>40</v>
+      </c>
+      <c r="B106" t="s">
+        <v>40</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E106" s="3"/>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A107" t="s">
+        <v>40</v>
+      </c>
+      <c r="B107" t="s">
+        <v>40</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E107" s="3"/>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A108" t="s">
+        <v>40</v>
+      </c>
+      <c r="B108" t="s">
+        <v>40</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A109" t="s">
+        <v>40</v>
+      </c>
+      <c r="B109" t="s">
+        <v>40</v>
+      </c>
+      <c r="C109" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E109" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A110" t="s">
+        <v>40</v>
+      </c>
+      <c r="B110" t="s">
+        <v>40</v>
+      </c>
+      <c r="C110" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E110" s="3"/>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A111" t="s">
+        <v>40</v>
+      </c>
+      <c r="B111" t="s">
+        <v>40</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E111" s="3"/>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A112" t="s">
+        <v>40</v>
+      </c>
+      <c r="B112" t="s">
+        <v>40</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E112" s="3"/>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A113" t="s">
+        <v>40</v>
+      </c>
+      <c r="B113" t="s">
+        <v>40</v>
+      </c>
+      <c r="C113" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E113" s="3"/>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A114" t="s">
+        <v>40</v>
+      </c>
+      <c r="B114" t="s">
+        <v>40</v>
+      </c>
+      <c r="C114" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A115" t="s">
+        <v>40</v>
+      </c>
+      <c r="B115" t="s">
+        <v>42</v>
+      </c>
+      <c r="C115" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A116" t="s">
+        <v>40</v>
+      </c>
+      <c r="B116" t="s">
+        <v>42</v>
+      </c>
+      <c r="C116" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A117" t="s">
+        <v>40</v>
+      </c>
+      <c r="B117" t="s">
+        <v>42</v>
+      </c>
+      <c r="C117" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A118" t="s">
+        <v>40</v>
+      </c>
+      <c r="B118" t="s">
+        <v>42</v>
+      </c>
+      <c r="C118" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A119" t="s">
+        <v>40</v>
+      </c>
+      <c r="B119" t="s">
+        <v>42</v>
+      </c>
+      <c r="C119" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A120" t="s">
+        <v>40</v>
+      </c>
+      <c r="B120" t="s">
+        <v>42</v>
+      </c>
+      <c r="C120" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A121" t="s">
+        <v>40</v>
+      </c>
+      <c r="B121" t="s">
+        <v>42</v>
+      </c>
+      <c r="C121" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A122" t="s">
+        <v>40</v>
+      </c>
+      <c r="B122" t="s">
+        <v>42</v>
+      </c>
+      <c r="C122" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -2293,70 +2678,92 @@
     <hyperlink ref="C19" r:id="rId35"/>
     <hyperlink ref="C11" r:id="rId36"/>
     <hyperlink ref="C12" r:id="rId37"/>
-    <hyperlink ref="C39" r:id="rId38"/>
-    <hyperlink ref="C40" r:id="rId39"/>
-    <hyperlink ref="C41" r:id="rId40"/>
-    <hyperlink ref="C42" r:id="rId41"/>
-    <hyperlink ref="C72" r:id="rId42"/>
-    <hyperlink ref="C73" r:id="rId43"/>
-    <hyperlink ref="C74" r:id="rId44"/>
-    <hyperlink ref="C43" r:id="rId45"/>
-    <hyperlink ref="C44" r:id="rId46"/>
-    <hyperlink ref="C45" r:id="rId47"/>
-    <hyperlink ref="C46" r:id="rId48"/>
-    <hyperlink ref="C47" r:id="rId49"/>
-    <hyperlink ref="C48" r:id="rId50"/>
-    <hyperlink ref="C49" r:id="rId51"/>
-    <hyperlink ref="C50" r:id="rId52"/>
-    <hyperlink ref="C51" r:id="rId53"/>
-    <hyperlink ref="C52" r:id="rId54"/>
-    <hyperlink ref="C53" r:id="rId55"/>
-    <hyperlink ref="C54" r:id="rId56"/>
-    <hyperlink ref="C55" r:id="rId57"/>
-    <hyperlink ref="C56" r:id="rId58"/>
-    <hyperlink ref="C57" r:id="rId59"/>
-    <hyperlink ref="C58" r:id="rId60"/>
-    <hyperlink ref="C59" r:id="rId61"/>
-    <hyperlink ref="C61" r:id="rId62"/>
-    <hyperlink ref="C62" r:id="rId63"/>
-    <hyperlink ref="C63" r:id="rId64"/>
-    <hyperlink ref="C64" r:id="rId65"/>
-    <hyperlink ref="C65" r:id="rId66"/>
-    <hyperlink ref="C66" r:id="rId67"/>
-    <hyperlink ref="C67" r:id="rId68"/>
-    <hyperlink ref="C68" r:id="rId69"/>
-    <hyperlink ref="C69" r:id="rId70"/>
-    <hyperlink ref="C70" r:id="rId71"/>
-    <hyperlink ref="C71" r:id="rId72"/>
-    <hyperlink ref="C60" r:id="rId73"/>
-    <hyperlink ref="C75" r:id="rId74"/>
-    <hyperlink ref="C76" r:id="rId75"/>
-    <hyperlink ref="C77" r:id="rId76"/>
-    <hyperlink ref="C78" r:id="rId77"/>
-    <hyperlink ref="C79" r:id="rId78"/>
-    <hyperlink ref="C80" r:id="rId79"/>
-    <hyperlink ref="C81" r:id="rId80"/>
-    <hyperlink ref="C82" r:id="rId81"/>
-    <hyperlink ref="C83" r:id="rId82"/>
-    <hyperlink ref="C84" r:id="rId83"/>
-    <hyperlink ref="C85" r:id="rId84"/>
-    <hyperlink ref="C86" r:id="rId85"/>
-    <hyperlink ref="C87" r:id="rId86"/>
-    <hyperlink ref="C88" r:id="rId87"/>
-    <hyperlink ref="C89" r:id="rId88"/>
-    <hyperlink ref="C90" r:id="rId89"/>
-    <hyperlink ref="C91" r:id="rId90"/>
-    <hyperlink ref="C92" r:id="rId91"/>
-    <hyperlink ref="C93" r:id="rId92"/>
-    <hyperlink ref="C94" r:id="rId93"/>
-    <hyperlink ref="C95" r:id="rId94"/>
-    <hyperlink ref="C96" r:id="rId95"/>
-    <hyperlink ref="C97" r:id="rId96"/>
-    <hyperlink ref="C98" r:id="rId97"/>
-    <hyperlink ref="C99" r:id="rId98"/>
-    <hyperlink ref="C100" r:id="rId99"/>
+    <hyperlink ref="C53" r:id="rId38"/>
+    <hyperlink ref="C54" r:id="rId39"/>
+    <hyperlink ref="C55" r:id="rId40"/>
+    <hyperlink ref="C56" r:id="rId41"/>
+    <hyperlink ref="C86" r:id="rId42"/>
+    <hyperlink ref="C87" r:id="rId43"/>
+    <hyperlink ref="C88" r:id="rId44"/>
+    <hyperlink ref="C57" r:id="rId45"/>
+    <hyperlink ref="C58" r:id="rId46"/>
+    <hyperlink ref="C59" r:id="rId47"/>
+    <hyperlink ref="C60" r:id="rId48"/>
+    <hyperlink ref="C61" r:id="rId49"/>
+    <hyperlink ref="C62" r:id="rId50"/>
+    <hyperlink ref="C63" r:id="rId51"/>
+    <hyperlink ref="C64" r:id="rId52"/>
+    <hyperlink ref="C65" r:id="rId53"/>
+    <hyperlink ref="C66" r:id="rId54"/>
+    <hyperlink ref="C67" r:id="rId55"/>
+    <hyperlink ref="C68" r:id="rId56"/>
+    <hyperlink ref="C69" r:id="rId57"/>
+    <hyperlink ref="C70" r:id="rId58"/>
+    <hyperlink ref="C71" r:id="rId59"/>
+    <hyperlink ref="C72" r:id="rId60"/>
+    <hyperlink ref="C73" r:id="rId61"/>
+    <hyperlink ref="C75" r:id="rId62"/>
+    <hyperlink ref="C76" r:id="rId63"/>
+    <hyperlink ref="C77" r:id="rId64"/>
+    <hyperlink ref="C78" r:id="rId65"/>
+    <hyperlink ref="C79" r:id="rId66"/>
+    <hyperlink ref="C80" r:id="rId67"/>
+    <hyperlink ref="C81" r:id="rId68"/>
+    <hyperlink ref="C82" r:id="rId69"/>
+    <hyperlink ref="C83" r:id="rId70"/>
+    <hyperlink ref="C84" r:id="rId71"/>
+    <hyperlink ref="C85" r:id="rId72"/>
+    <hyperlink ref="C74" r:id="rId73"/>
+    <hyperlink ref="C89" r:id="rId74"/>
+    <hyperlink ref="C90" r:id="rId75"/>
+    <hyperlink ref="C91" r:id="rId76"/>
+    <hyperlink ref="C92" r:id="rId77"/>
+    <hyperlink ref="C93" r:id="rId78"/>
+    <hyperlink ref="C94" r:id="rId79"/>
+    <hyperlink ref="C95" r:id="rId80"/>
+    <hyperlink ref="C96" r:id="rId81"/>
+    <hyperlink ref="C97" r:id="rId82"/>
+    <hyperlink ref="C98" r:id="rId83"/>
+    <hyperlink ref="C99" r:id="rId84"/>
+    <hyperlink ref="C100" r:id="rId85"/>
+    <hyperlink ref="C101" r:id="rId86"/>
+    <hyperlink ref="C102" r:id="rId87"/>
+    <hyperlink ref="C103" r:id="rId88"/>
+    <hyperlink ref="C104" r:id="rId89"/>
+    <hyperlink ref="C105" r:id="rId90"/>
+    <hyperlink ref="C106" r:id="rId91"/>
+    <hyperlink ref="C107" r:id="rId92"/>
+    <hyperlink ref="C108" r:id="rId93"/>
+    <hyperlink ref="C109" r:id="rId94"/>
+    <hyperlink ref="C110" r:id="rId95"/>
+    <hyperlink ref="C111" r:id="rId96"/>
+    <hyperlink ref="C112" r:id="rId97"/>
+    <hyperlink ref="C113" r:id="rId98"/>
+    <hyperlink ref="C114" r:id="rId99"/>
+    <hyperlink ref="C39" r:id="rId100"/>
+    <hyperlink ref="C40" r:id="rId101"/>
+    <hyperlink ref="C41" r:id="rId102"/>
+    <hyperlink ref="C42" r:id="rId103"/>
+    <hyperlink ref="C43" r:id="rId104"/>
+    <hyperlink ref="C44" r:id="rId105"/>
+    <hyperlink ref="C45" r:id="rId106"/>
+    <hyperlink ref="C46" r:id="rId107"/>
+    <hyperlink ref="C47" r:id="rId108"/>
+    <hyperlink ref="C48" r:id="rId109"/>
+    <hyperlink ref="C49" r:id="rId110"/>
+    <hyperlink ref="C50" r:id="rId111"/>
+    <hyperlink ref="C51" r:id="rId112"/>
+    <hyperlink ref="C52" r:id="rId113"/>
+    <hyperlink ref="C115" r:id="rId114"/>
+    <hyperlink ref="C116" r:id="rId115"/>
+    <hyperlink ref="C117" r:id="rId116"/>
+    <hyperlink ref="C118" r:id="rId117"/>
+    <hyperlink ref="C119" r:id="rId118"/>
+    <hyperlink ref="C120" r:id="rId119"/>
+    <hyperlink ref="C121" r:id="rId120"/>
+    <hyperlink ref="C122" r:id="rId121"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId100"/>
+  <pageSetup orientation="portrait" r:id="rId122"/>
 </worksheet>
 </file>
--- a/data/running_lists.xlsx
+++ b/data/running_lists.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PhuLH7\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FB-Affiliate-Bot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="11650" windowHeight="4780"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9192"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -798,16 +798,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E122"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="50.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="50.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -824,7 +824,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>40</v>
       </c>
@@ -839,7 +839,7 @@
       </c>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>40</v>
       </c>
@@ -856,7 +856,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>40</v>
       </c>
@@ -871,7 +871,7 @@
       </c>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>40</v>
       </c>
@@ -886,7 +886,7 @@
       </c>
       <c r="E5" s="3"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>40</v>
       </c>
@@ -903,7 +903,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>40</v>
       </c>
@@ -920,7 +920,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>40</v>
       </c>
@@ -937,7 +937,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>40</v>
       </c>
@@ -954,7 +954,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>40</v>
       </c>
@@ -971,7 +971,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>40</v>
       </c>
@@ -988,7 +988,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>40</v>
       </c>
@@ -1005,7 +1005,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>40</v>
       </c>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="E13" s="3"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -1037,7 +1037,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>40</v>
       </c>
@@ -1054,7 +1054,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>40</v>
       </c>
@@ -1071,7 +1071,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -1088,7 +1088,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -1105,7 +1105,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>40</v>
       </c>
@@ -1122,7 +1122,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>40</v>
       </c>
@@ -1139,7 +1139,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>40</v>
       </c>
@@ -1156,7 +1156,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>40</v>
       </c>
@@ -1173,7 +1173,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -1190,7 +1190,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>40</v>
       </c>
@@ -1207,7 +1207,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>40</v>
       </c>
@@ -1224,7 +1224,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>40</v>
       </c>
@@ -1241,7 +1241,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>40</v>
       </c>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E27" s="3"/>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>40</v>
       </c>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="E28" s="3"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -1288,7 +1288,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>40</v>
       </c>
@@ -1305,7 +1305,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>40</v>
       </c>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="E31" s="3"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>40</v>
       </c>
@@ -1337,7 +1337,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>40</v>
       </c>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="E33" s="3"/>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>40</v>
       </c>
@@ -1369,7 +1369,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>40</v>
       </c>
@@ -1386,7 +1386,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>40</v>
       </c>
@@ -1403,7 +1403,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>40</v>
       </c>
@@ -1420,7 +1420,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>40</v>
       </c>
@@ -1437,7 +1437,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>40</v>
       </c>
@@ -1452,22 +1452,22 @@
       </c>
       <c r="E39" s="3"/>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>40</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>83</v>
       </c>
       <c r="E40" s="3"/>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>40</v>
       </c>
@@ -1475,14 +1475,14 @@
         <v>41</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>83</v>
       </c>
       <c r="E41" s="3"/>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>40</v>
       </c>
@@ -1490,14 +1490,14 @@
         <v>41</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>83</v>
       </c>
       <c r="E42" s="3"/>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>40</v>
       </c>
@@ -1505,149 +1505,131 @@
         <v>41</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>83</v>
       </c>
       <c r="E43" s="3"/>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
-        <v>40</v>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" s="3" t="s">
+        <v>80</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>83</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="D44" s="2"/>
       <c r="E44" s="3"/>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
-        <v>40</v>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" s="3" t="s">
+        <v>80</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>83</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="D45" s="2"/>
       <c r="E45" s="3"/>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
-        <v>40</v>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46" s="3" t="s">
+        <v>80</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>83</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="D46" s="2"/>
       <c r="E46" s="3"/>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
-        <v>40</v>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" s="3" t="s">
+        <v>80</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>83</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="D47" s="2"/>
       <c r="E47" s="3"/>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
-        <v>40</v>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" s="3" t="s">
+        <v>80</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>83</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="D48" s="2"/>
       <c r="E48" s="3"/>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
-        <v>40</v>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49" s="3" t="s">
+        <v>80</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>83</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="D49" s="2"/>
       <c r="E49" s="3"/>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
-        <v>40</v>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50" s="3" t="s">
+        <v>80</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>83</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="D50" s="2"/>
       <c r="E50" s="3"/>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
-        <v>40</v>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51" s="3" t="s">
+        <v>80</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>83</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="D51" s="2"/>
       <c r="E51" s="3"/>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
-        <v>40</v>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" s="3" t="s">
+        <v>80</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>83</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="D52" s="2"/>
       <c r="E52" s="3"/>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
         <v>80</v>
       </c>
@@ -1655,12 +1637,12 @@
         <v>80</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="D53" s="2"/>
       <c r="E53" s="3"/>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>80</v>
       </c>
@@ -1668,12 +1650,12 @@
         <v>80</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" s="3"/>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
         <v>80</v>
       </c>
@@ -1681,12 +1663,12 @@
         <v>80</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" s="3"/>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>80</v>
       </c>
@@ -1694,12 +1676,12 @@
         <v>80</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="D56" s="2"/>
       <c r="E56" s="3"/>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>80</v>
       </c>
@@ -1707,12 +1689,12 @@
         <v>80</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" s="3"/>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
         <v>80</v>
       </c>
@@ -1720,12 +1702,12 @@
         <v>80</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="3"/>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
         <v>80</v>
       </c>
@@ -1733,12 +1715,12 @@
         <v>80</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="D59" s="2"/>
       <c r="E59" s="3"/>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
         <v>80</v>
       </c>
@@ -1746,12 +1728,12 @@
         <v>80</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="D60" s="2"/>
       <c r="E60" s="3"/>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
         <v>80</v>
       </c>
@@ -1759,12 +1741,12 @@
         <v>80</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" s="3"/>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
         <v>80</v>
       </c>
@@ -1772,12 +1754,12 @@
         <v>80</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="D62" s="2"/>
       <c r="E62" s="3"/>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
         <v>80</v>
       </c>
@@ -1785,12 +1767,12 @@
         <v>80</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="D63" s="2"/>
       <c r="E63" s="3"/>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
         <v>80</v>
       </c>
@@ -1798,12 +1780,12 @@
         <v>80</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="D64" s="2"/>
       <c r="E64" s="3"/>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
         <v>80</v>
       </c>
@@ -1811,12 +1793,12 @@
         <v>80</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="D65" s="2"/>
       <c r="E65" s="3"/>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
         <v>80</v>
       </c>
@@ -1824,12 +1806,12 @@
         <v>80</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="D66" s="2"/>
       <c r="E66" s="3"/>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
         <v>80</v>
       </c>
@@ -1837,12 +1819,12 @@
         <v>80</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="D67" s="2"/>
       <c r="E67" s="3"/>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
         <v>80</v>
       </c>
@@ -1850,12 +1832,12 @@
         <v>80</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D68" s="2"/>
       <c r="E68" s="3"/>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
         <v>80</v>
       </c>
@@ -1863,12 +1845,12 @@
         <v>80</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="D69" s="2"/>
       <c r="E69" s="3"/>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
         <v>80</v>
       </c>
@@ -1876,12 +1858,12 @@
         <v>80</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="D70" s="2"/>
       <c r="E70" s="3"/>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
         <v>80</v>
       </c>
@@ -1889,12 +1871,12 @@
         <v>80</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="D71" s="2"/>
       <c r="E71" s="3"/>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
         <v>80</v>
       </c>
@@ -1902,12 +1884,12 @@
         <v>80</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="D72" s="2"/>
       <c r="E72" s="3"/>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
         <v>80</v>
       </c>
@@ -1915,12 +1897,12 @@
         <v>80</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="D73" s="2"/>
       <c r="E73" s="3"/>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
         <v>80</v>
       </c>
@@ -1928,12 +1910,12 @@
         <v>80</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" s="3"/>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
         <v>80</v>
       </c>
@@ -1941,12 +1923,12 @@
         <v>80</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" s="3"/>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
         <v>80</v>
       </c>
@@ -1954,168 +1936,196 @@
         <v>80</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="D76" s="2"/>
       <c r="E76" s="3"/>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
         <v>80</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" s="3"/>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
         <v>80</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" s="3"/>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
         <v>80</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" s="3"/>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A80" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C80" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D80" s="2"/>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>40</v>
+      </c>
+      <c r="B80" t="s">
+        <v>40</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>104</v>
+      </c>
       <c r="E80" s="3"/>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A81" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C81" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="D81" s="2"/>
-      <c r="E81" s="3"/>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A82" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C82" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D82" s="2"/>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>40</v>
+      </c>
+      <c r="B81" t="s">
+        <v>40</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>40</v>
+      </c>
+      <c r="B82" t="s">
+        <v>40</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>104</v>
+      </c>
       <c r="E82" s="3"/>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A83" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C83" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="D83" s="2"/>
-      <c r="E83" s="3"/>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A84" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C84" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="D84" s="2"/>
-      <c r="E84" s="3"/>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A85" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C85" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="D85" s="2"/>
-      <c r="E85" s="3"/>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A86" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C86" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="D86" s="2"/>
-      <c r="E86" s="3"/>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A87" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C87" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="D87" s="2"/>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>40</v>
+      </c>
+      <c r="B83" t="s">
+        <v>40</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>40</v>
+      </c>
+      <c r="B84" t="s">
+        <v>40</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>40</v>
+      </c>
+      <c r="B85" t="s">
+        <v>40</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>40</v>
+      </c>
+      <c r="B86" t="s">
+        <v>40</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>40</v>
+      </c>
+      <c r="B87" t="s">
+        <v>40</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>104</v>
+      </c>
       <c r="E87" s="3"/>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A88" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B88" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C88" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="D88" s="2"/>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>40</v>
+      </c>
+      <c r="B88" t="s">
+        <v>40</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>104</v>
+      </c>
       <c r="E88" s="3"/>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>40</v>
       </c>
@@ -2123,14 +2133,14 @@
         <v>40</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="D89" s="3" t="s">
-        <v>104</v>
+        <v>94</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="E89" s="3"/>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>40</v>
       </c>
@@ -2138,31 +2148,29 @@
         <v>40</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="D90" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E90" s="3"/>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>40</v>
+      </c>
+      <c r="B91" t="s">
+        <v>40</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D91" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E90" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A91" t="s">
-        <v>40</v>
-      </c>
-      <c r="B91" t="s">
-        <v>40</v>
-      </c>
-      <c r="C91" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>104</v>
-      </c>
       <c r="E91" s="3"/>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>40</v>
       </c>
@@ -2170,7 +2178,7 @@
         <v>40</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>106</v>
@@ -2179,7 +2187,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>40</v>
       </c>
@@ -2187,33 +2195,31 @@
         <v>40</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D93" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E93" s="3"/>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>40</v>
+      </c>
+      <c r="B94" t="s">
+        <v>40</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D94" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="E93" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A94" t="s">
-        <v>40</v>
-      </c>
-      <c r="B94" t="s">
-        <v>40</v>
-      </c>
-      <c r="C94" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>85</v>
-      </c>
       <c r="E94" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>40</v>
       </c>
@@ -2221,7 +2227,7 @@
         <v>40</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>91</v>
+        <v>27</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>85</v>
@@ -2230,7 +2236,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>40</v>
       </c>
@@ -2238,14 +2244,14 @@
         <v>40</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="E96" s="3"/>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>40</v>
       </c>
@@ -2253,14 +2259,14 @@
         <v>40</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>93</v>
+        <v>39</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="E97" s="3"/>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>40</v>
       </c>
@@ -2268,29 +2274,31 @@
         <v>40</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D98" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E98" s="3"/>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>40</v>
+      </c>
+      <c r="B99" t="s">
+        <v>40</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D99" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E98" s="3"/>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A99" t="s">
-        <v>40</v>
-      </c>
-      <c r="B99" t="s">
-        <v>40</v>
-      </c>
-      <c r="C99" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E99" s="3"/>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E99" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>40</v>
       </c>
@@ -2298,14 +2306,16 @@
         <v>40</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E100" s="3"/>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
+        <v>8</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>40</v>
       </c>
@@ -2313,16 +2323,14 @@
         <v>40</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="D101" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
+        <v>101</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E101" s="3"/>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>40</v>
       </c>
@@ -2330,14 +2338,14 @@
         <v>40</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>104</v>
       </c>
       <c r="E102" s="3"/>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>40</v>
       </c>
@@ -2345,16 +2353,14 @@
         <v>40</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D103" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="E103" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
+        <v>11</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E103" s="3"/>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>40</v>
       </c>
@@ -2362,16 +2368,14 @@
         <v>40</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E104" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
+        <v>104</v>
+      </c>
+      <c r="E104" s="3"/>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>40</v>
       </c>
@@ -2379,265 +2383,269 @@
         <v>40</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E105" s="3"/>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E105" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>40</v>
       </c>
       <c r="B106" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>39</v>
+        <v>122</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>85</v>
       </c>
       <c r="E106" s="3"/>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>40</v>
       </c>
       <c r="B107" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>99</v>
+        <v>9</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="E107" s="3"/>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>40</v>
       </c>
       <c r="B108" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E108" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E108" s="3"/>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>40</v>
       </c>
       <c r="B109" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D109" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="E109" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
+        <v>124</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E109" s="3"/>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>40</v>
       </c>
       <c r="B110" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="E110" s="3"/>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>40</v>
       </c>
       <c r="B111" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>6</v>
+        <v>126</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="E111" s="3"/>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>40</v>
       </c>
       <c r="B112" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>11</v>
+        <v>127</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="E112" s="3"/>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>40</v>
       </c>
       <c r="B113" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="E113" s="3"/>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>40</v>
       </c>
-      <c r="B114" t="s">
-        <v>40</v>
-      </c>
-      <c r="C114" s="4" t="s">
-        <v>103</v>
+      <c r="B114" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C114" s="6" t="s">
+        <v>109</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E114" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E114" s="3"/>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>40</v>
       </c>
-      <c r="B115" t="s">
-        <v>42</v>
-      </c>
-      <c r="C115" s="4" t="s">
-        <v>122</v>
+      <c r="B115" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C115" s="6" t="s">
+        <v>110</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E115" s="3"/>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>40</v>
       </c>
-      <c r="B116" t="s">
-        <v>42</v>
-      </c>
-      <c r="C116" s="4" t="s">
-        <v>9</v>
+      <c r="B116" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C116" s="6" t="s">
+        <v>111</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E116" s="3"/>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>40</v>
       </c>
-      <c r="B117" t="s">
-        <v>42</v>
-      </c>
-      <c r="C117" s="4" t="s">
-        <v>123</v>
+      <c r="B117" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C117" s="6" t="s">
+        <v>112</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E117" s="3"/>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>40</v>
       </c>
-      <c r="B118" t="s">
-        <v>42</v>
-      </c>
-      <c r="C118" s="4" t="s">
-        <v>124</v>
+      <c r="B118" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C118" s="6" t="s">
+        <v>113</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E118" s="3"/>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>40</v>
       </c>
-      <c r="B119" t="s">
-        <v>42</v>
-      </c>
-      <c r="C119" s="4" t="s">
-        <v>125</v>
+      <c r="B119" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C119" s="6" t="s">
+        <v>114</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E119" s="3"/>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>40</v>
       </c>
-      <c r="B120" t="s">
-        <v>42</v>
-      </c>
-      <c r="C120" s="4" t="s">
-        <v>126</v>
+      <c r="B120" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C120" s="6" t="s">
+        <v>115</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E120" s="3"/>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>40</v>
       </c>
-      <c r="B121" t="s">
-        <v>42</v>
-      </c>
-      <c r="C121" s="4" t="s">
-        <v>127</v>
+      <c r="B121" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C121" s="6" t="s">
+        <v>116</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E121" s="3"/>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>40</v>
       </c>
-      <c r="B122" t="s">
-        <v>42</v>
-      </c>
-      <c r="C122" s="4" t="s">
-        <v>128</v>
+      <c r="B122" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C122" s="6" t="s">
+        <v>117</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>85</v>
       </c>
+      <c r="E122" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -2678,90 +2686,90 @@
     <hyperlink ref="C19" r:id="rId35"/>
     <hyperlink ref="C11" r:id="rId36"/>
     <hyperlink ref="C12" r:id="rId37"/>
-    <hyperlink ref="C53" r:id="rId38"/>
-    <hyperlink ref="C54" r:id="rId39"/>
-    <hyperlink ref="C55" r:id="rId40"/>
-    <hyperlink ref="C56" r:id="rId41"/>
-    <hyperlink ref="C86" r:id="rId42"/>
-    <hyperlink ref="C87" r:id="rId43"/>
-    <hyperlink ref="C88" r:id="rId44"/>
-    <hyperlink ref="C57" r:id="rId45"/>
-    <hyperlink ref="C58" r:id="rId46"/>
-    <hyperlink ref="C59" r:id="rId47"/>
-    <hyperlink ref="C60" r:id="rId48"/>
-    <hyperlink ref="C61" r:id="rId49"/>
-    <hyperlink ref="C62" r:id="rId50"/>
-    <hyperlink ref="C63" r:id="rId51"/>
-    <hyperlink ref="C64" r:id="rId52"/>
-    <hyperlink ref="C65" r:id="rId53"/>
-    <hyperlink ref="C66" r:id="rId54"/>
-    <hyperlink ref="C67" r:id="rId55"/>
-    <hyperlink ref="C68" r:id="rId56"/>
-    <hyperlink ref="C69" r:id="rId57"/>
-    <hyperlink ref="C70" r:id="rId58"/>
-    <hyperlink ref="C71" r:id="rId59"/>
-    <hyperlink ref="C72" r:id="rId60"/>
-    <hyperlink ref="C73" r:id="rId61"/>
-    <hyperlink ref="C75" r:id="rId62"/>
-    <hyperlink ref="C76" r:id="rId63"/>
-    <hyperlink ref="C77" r:id="rId64"/>
-    <hyperlink ref="C78" r:id="rId65"/>
-    <hyperlink ref="C79" r:id="rId66"/>
-    <hyperlink ref="C80" r:id="rId67"/>
-    <hyperlink ref="C81" r:id="rId68"/>
-    <hyperlink ref="C82" r:id="rId69"/>
-    <hyperlink ref="C83" r:id="rId70"/>
-    <hyperlink ref="C84" r:id="rId71"/>
-    <hyperlink ref="C85" r:id="rId72"/>
-    <hyperlink ref="C74" r:id="rId73"/>
-    <hyperlink ref="C89" r:id="rId74"/>
-    <hyperlink ref="C90" r:id="rId75"/>
-    <hyperlink ref="C91" r:id="rId76"/>
-    <hyperlink ref="C92" r:id="rId77"/>
-    <hyperlink ref="C93" r:id="rId78"/>
-    <hyperlink ref="C94" r:id="rId79"/>
-    <hyperlink ref="C95" r:id="rId80"/>
-    <hyperlink ref="C96" r:id="rId81"/>
-    <hyperlink ref="C97" r:id="rId82"/>
-    <hyperlink ref="C98" r:id="rId83"/>
-    <hyperlink ref="C99" r:id="rId84"/>
-    <hyperlink ref="C100" r:id="rId85"/>
-    <hyperlink ref="C101" r:id="rId86"/>
-    <hyperlink ref="C102" r:id="rId87"/>
-    <hyperlink ref="C103" r:id="rId88"/>
-    <hyperlink ref="C104" r:id="rId89"/>
-    <hyperlink ref="C105" r:id="rId90"/>
-    <hyperlink ref="C106" r:id="rId91"/>
-    <hyperlink ref="C107" r:id="rId92"/>
-    <hyperlink ref="C108" r:id="rId93"/>
-    <hyperlink ref="C109" r:id="rId94"/>
-    <hyperlink ref="C110" r:id="rId95"/>
-    <hyperlink ref="C111" r:id="rId96"/>
-    <hyperlink ref="C112" r:id="rId97"/>
-    <hyperlink ref="C113" r:id="rId98"/>
-    <hyperlink ref="C114" r:id="rId99"/>
+    <hyperlink ref="C44" r:id="rId38"/>
+    <hyperlink ref="C45" r:id="rId39"/>
+    <hyperlink ref="C46" r:id="rId40"/>
+    <hyperlink ref="C47" r:id="rId41"/>
+    <hyperlink ref="C77" r:id="rId42"/>
+    <hyperlink ref="C78" r:id="rId43"/>
+    <hyperlink ref="C79" r:id="rId44"/>
+    <hyperlink ref="C48" r:id="rId45"/>
+    <hyperlink ref="C49" r:id="rId46"/>
+    <hyperlink ref="C50" r:id="rId47"/>
+    <hyperlink ref="C51" r:id="rId48"/>
+    <hyperlink ref="C52" r:id="rId49"/>
+    <hyperlink ref="C53" r:id="rId50"/>
+    <hyperlink ref="C54" r:id="rId51"/>
+    <hyperlink ref="C55" r:id="rId52"/>
+    <hyperlink ref="C56" r:id="rId53"/>
+    <hyperlink ref="C57" r:id="rId54"/>
+    <hyperlink ref="C58" r:id="rId55"/>
+    <hyperlink ref="C59" r:id="rId56"/>
+    <hyperlink ref="C60" r:id="rId57"/>
+    <hyperlink ref="C61" r:id="rId58"/>
+    <hyperlink ref="C62" r:id="rId59"/>
+    <hyperlink ref="C63" r:id="rId60"/>
+    <hyperlink ref="C64" r:id="rId61"/>
+    <hyperlink ref="C66" r:id="rId62"/>
+    <hyperlink ref="C67" r:id="rId63"/>
+    <hyperlink ref="C68" r:id="rId64"/>
+    <hyperlink ref="C69" r:id="rId65"/>
+    <hyperlink ref="C70" r:id="rId66"/>
+    <hyperlink ref="C71" r:id="rId67"/>
+    <hyperlink ref="C72" r:id="rId68"/>
+    <hyperlink ref="C73" r:id="rId69"/>
+    <hyperlink ref="C74" r:id="rId70"/>
+    <hyperlink ref="C75" r:id="rId71"/>
+    <hyperlink ref="C76" r:id="rId72"/>
+    <hyperlink ref="C65" r:id="rId73"/>
+    <hyperlink ref="C80" r:id="rId74"/>
+    <hyperlink ref="C81" r:id="rId75"/>
+    <hyperlink ref="C82" r:id="rId76"/>
+    <hyperlink ref="C83" r:id="rId77"/>
+    <hyperlink ref="C84" r:id="rId78"/>
+    <hyperlink ref="C85" r:id="rId79"/>
+    <hyperlink ref="C86" r:id="rId80"/>
+    <hyperlink ref="C87" r:id="rId81"/>
+    <hyperlink ref="C88" r:id="rId82"/>
+    <hyperlink ref="C89" r:id="rId83"/>
+    <hyperlink ref="C90" r:id="rId84"/>
+    <hyperlink ref="C91" r:id="rId85"/>
+    <hyperlink ref="C92" r:id="rId86"/>
+    <hyperlink ref="C93" r:id="rId87"/>
+    <hyperlink ref="C94" r:id="rId88"/>
+    <hyperlink ref="C95" r:id="rId89"/>
+    <hyperlink ref="C96" r:id="rId90"/>
+    <hyperlink ref="C97" r:id="rId91"/>
+    <hyperlink ref="C98" r:id="rId92"/>
+    <hyperlink ref="C99" r:id="rId93"/>
+    <hyperlink ref="C100" r:id="rId94"/>
+    <hyperlink ref="C101" r:id="rId95"/>
+    <hyperlink ref="C102" r:id="rId96"/>
+    <hyperlink ref="C103" r:id="rId97"/>
+    <hyperlink ref="C104" r:id="rId98"/>
+    <hyperlink ref="C105" r:id="rId99"/>
     <hyperlink ref="C39" r:id="rId100"/>
-    <hyperlink ref="C40" r:id="rId101"/>
-    <hyperlink ref="C41" r:id="rId102"/>
-    <hyperlink ref="C42" r:id="rId103"/>
-    <hyperlink ref="C43" r:id="rId104"/>
-    <hyperlink ref="C44" r:id="rId105"/>
-    <hyperlink ref="C45" r:id="rId106"/>
-    <hyperlink ref="C46" r:id="rId107"/>
-    <hyperlink ref="C47" r:id="rId108"/>
-    <hyperlink ref="C48" r:id="rId109"/>
-    <hyperlink ref="C49" r:id="rId110"/>
-    <hyperlink ref="C50" r:id="rId111"/>
-    <hyperlink ref="C51" r:id="rId112"/>
-    <hyperlink ref="C52" r:id="rId113"/>
-    <hyperlink ref="C115" r:id="rId114"/>
-    <hyperlink ref="C116" r:id="rId115"/>
-    <hyperlink ref="C117" r:id="rId116"/>
-    <hyperlink ref="C118" r:id="rId117"/>
-    <hyperlink ref="C119" r:id="rId118"/>
-    <hyperlink ref="C120" r:id="rId119"/>
-    <hyperlink ref="C121" r:id="rId120"/>
-    <hyperlink ref="C122" r:id="rId121"/>
+    <hyperlink ref="C114" r:id="rId101"/>
+    <hyperlink ref="C115" r:id="rId102"/>
+    <hyperlink ref="C116" r:id="rId103"/>
+    <hyperlink ref="C117" r:id="rId104"/>
+    <hyperlink ref="C118" r:id="rId105"/>
+    <hyperlink ref="C119" r:id="rId106"/>
+    <hyperlink ref="C120" r:id="rId107"/>
+    <hyperlink ref="C121" r:id="rId108"/>
+    <hyperlink ref="C122" r:id="rId109"/>
+    <hyperlink ref="C40" r:id="rId110"/>
+    <hyperlink ref="C41" r:id="rId111"/>
+    <hyperlink ref="C42" r:id="rId112"/>
+    <hyperlink ref="C43" r:id="rId113"/>
+    <hyperlink ref="C106" r:id="rId114"/>
+    <hyperlink ref="C107" r:id="rId115"/>
+    <hyperlink ref="C108" r:id="rId116"/>
+    <hyperlink ref="C109" r:id="rId117"/>
+    <hyperlink ref="C110" r:id="rId118"/>
+    <hyperlink ref="C111" r:id="rId119"/>
+    <hyperlink ref="C112" r:id="rId120"/>
+    <hyperlink ref="C113" r:id="rId121"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId122"/>

--- a/data/running_lists.xlsx
+++ b/data/running_lists.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FB-Affiliate-Bot\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AIML_Usecases\ai-comment-bot-main\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9192"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9190"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="142">
   <si>
     <t>Link</t>
   </si>
@@ -411,6 +411,45 @@
   </si>
   <si>
     <t>https://www.facebook.com/groups/25013110648385195/</t>
+  </si>
+  <si>
+    <t>Joined</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/groups/vinfastlimogreenclubvn/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/groups/363868249987338/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/groups/limogreenvn/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/groups/taxixanhvinfastsm</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/groups/clubkiavn/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/groups/695793050774841/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/groups/1813175750115872</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/groups/736863345505798/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/groups/1462644071487886/</t>
+  </si>
+  <si>
+    <t>https://www.facebook.com/groups/736371176176261/</t>
+  </si>
+  <si>
+    <t>Limo Green</t>
+  </si>
+  <si>
+    <t>Mac Author</t>
   </si>
 </sst>
 </file>
@@ -461,7 +500,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -497,13 +536,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -515,6 +565,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="2" applyBorder="1"/>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
@@ -797,17 +849,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E122"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F132"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="50.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="50.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.36328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -823,8 +876,11 @@
       <c r="E1" s="1" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F1" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>40</v>
       </c>
@@ -838,8 +894,9 @@
         <v>104</v>
       </c>
       <c r="E2" s="3"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F2" s="3"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>40</v>
       </c>
@@ -855,8 +912,9 @@
       <c r="E3" s="3" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F3" s="3"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>40</v>
       </c>
@@ -870,8 +928,9 @@
         <v>104</v>
       </c>
       <c r="E4" s="3"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F4" s="3"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>40</v>
       </c>
@@ -885,8 +944,9 @@
         <v>104</v>
       </c>
       <c r="E5" s="3"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F5" s="3"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>40</v>
       </c>
@@ -902,8 +962,9 @@
       <c r="E6" s="3" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F6" s="3"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>40</v>
       </c>
@@ -919,8 +980,9 @@
       <c r="E7" s="3" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F7" s="3"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>40</v>
       </c>
@@ -936,8 +998,9 @@
       <c r="E8" s="3" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F8" s="3"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>40</v>
       </c>
@@ -953,8 +1016,9 @@
       <c r="E9" s="3" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F9" s="3"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>40</v>
       </c>
@@ -970,8 +1034,9 @@
       <c r="E10" s="3" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F10" s="3"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>40</v>
       </c>
@@ -987,8 +1052,9 @@
       <c r="E11" s="3" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F11" s="3"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>40</v>
       </c>
@@ -1004,8 +1070,9 @@
       <c r="E12" s="3" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F12" s="3"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>40</v>
       </c>
@@ -1019,8 +1086,9 @@
         <v>104</v>
       </c>
       <c r="E13" s="3"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F13" s="3"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -1036,8 +1104,9 @@
       <c r="E14" s="3" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F14" s="3"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>40</v>
       </c>
@@ -1053,8 +1122,9 @@
       <c r="E15" s="3" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F15" s="3"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>40</v>
       </c>
@@ -1070,8 +1140,9 @@
       <c r="E16" s="3" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F16" s="3"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>40</v>
       </c>
@@ -1087,8 +1158,9 @@
       <c r="E17" s="3" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F17" s="3"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>40</v>
       </c>
@@ -1104,8 +1176,9 @@
       <c r="E18" s="3" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F18" s="3"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>40</v>
       </c>
@@ -1121,8 +1194,9 @@
       <c r="E19" s="3" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F19" s="3"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>40</v>
       </c>
@@ -1133,13 +1207,14 @@
         <v>22</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+      <c r="F20" s="3"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>40</v>
       </c>
@@ -1155,8 +1230,9 @@
       <c r="E21" s="3" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F21" s="3"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>40</v>
       </c>
@@ -1172,8 +1248,9 @@
       <c r="E22" s="3" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F22" s="3"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>40</v>
       </c>
@@ -1189,8 +1266,9 @@
       <c r="E23" s="3" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F23" s="3"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>40</v>
       </c>
@@ -1206,8 +1284,9 @@
       <c r="E24" s="3" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F24" s="3"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>40</v>
       </c>
@@ -1223,8 +1302,9 @@
       <c r="E25" s="3" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F25" s="3"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>40</v>
       </c>
@@ -1235,13 +1315,14 @@
         <v>28</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+      <c r="F26" s="3"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>40</v>
       </c>
@@ -1252,11 +1333,12 @@
         <v>29</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="E27" s="3"/>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F27" s="3"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>40</v>
       </c>
@@ -1270,8 +1352,9 @@
         <v>104</v>
       </c>
       <c r="E28" s="3"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F28" s="3"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -1287,8 +1370,9 @@
       <c r="E29" s="3" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F29" s="3"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>40</v>
       </c>
@@ -1299,13 +1383,14 @@
         <v>32</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F30" s="3"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>40</v>
       </c>
@@ -1319,8 +1404,9 @@
         <v>104</v>
       </c>
       <c r="E31" s="3"/>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F31" s="3"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>40</v>
       </c>
@@ -1336,8 +1422,9 @@
       <c r="E32" s="3" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F32" s="3"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>40</v>
       </c>
@@ -1351,8 +1438,9 @@
         <v>104</v>
       </c>
       <c r="E33" s="3"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F33" s="3"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>40</v>
       </c>
@@ -1368,8 +1456,9 @@
       <c r="E34" s="3" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F34" s="3"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>40</v>
       </c>
@@ -1385,8 +1474,9 @@
       <c r="E35" s="3" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F35" s="3"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>40</v>
       </c>
@@ -1402,8 +1492,9 @@
       <c r="E36" s="3" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F36" s="3"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>40</v>
       </c>
@@ -1419,8 +1510,9 @@
       <c r="E37" s="3" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F37" s="3"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>40</v>
       </c>
@@ -1436,8 +1528,9 @@
       <c r="E38" s="3" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F38" s="3"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>40</v>
       </c>
@@ -1451,8 +1544,9 @@
         <v>83</v>
       </c>
       <c r="E39" s="3"/>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F39" s="3"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>40</v>
       </c>
@@ -1463,11 +1557,14 @@
         <v>118</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E40" s="3"/>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F40" s="3"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>40</v>
       </c>
@@ -1481,8 +1578,9 @@
         <v>83</v>
       </c>
       <c r="E41" s="3"/>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F41" s="3"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>40</v>
       </c>
@@ -1496,8 +1594,9 @@
         <v>83</v>
       </c>
       <c r="E42" s="3"/>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F42" s="3"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>40</v>
       </c>
@@ -1511,8 +1610,9 @@
         <v>83</v>
       </c>
       <c r="E43" s="3"/>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F43" s="3"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
         <v>80</v>
       </c>
@@ -1524,8 +1624,9 @@
       </c>
       <c r="D44" s="2"/>
       <c r="E44" s="3"/>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F44" s="3"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
         <v>80</v>
       </c>
@@ -1537,8 +1638,9 @@
       </c>
       <c r="D45" s="2"/>
       <c r="E45" s="3"/>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F45" s="3"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" s="3" t="s">
         <v>80</v>
       </c>
@@ -1550,8 +1652,9 @@
       </c>
       <c r="D46" s="2"/>
       <c r="E46" s="3"/>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F46" s="3"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" s="3" t="s">
         <v>80</v>
       </c>
@@ -1563,8 +1666,9 @@
       </c>
       <c r="D47" s="2"/>
       <c r="E47" s="3"/>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F47" s="3"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="3" t="s">
         <v>80</v>
       </c>
@@ -1576,8 +1680,9 @@
       </c>
       <c r="D48" s="2"/>
       <c r="E48" s="3"/>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F48" s="3"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="3" t="s">
         <v>80</v>
       </c>
@@ -1589,8 +1694,9 @@
       </c>
       <c r="D49" s="2"/>
       <c r="E49" s="3"/>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F49" s="3"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="3" t="s">
         <v>80</v>
       </c>
@@ -1602,8 +1708,9 @@
       </c>
       <c r="D50" s="2"/>
       <c r="E50" s="3"/>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F50" s="3"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="3" t="s">
         <v>80</v>
       </c>
@@ -1615,8 +1722,9 @@
       </c>
       <c r="D51" s="2"/>
       <c r="E51" s="3"/>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F51" s="3"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="3" t="s">
         <v>80</v>
       </c>
@@ -1628,8 +1736,9 @@
       </c>
       <c r="D52" s="2"/>
       <c r="E52" s="3"/>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F52" s="3"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="3" t="s">
         <v>80</v>
       </c>
@@ -1641,8 +1750,9 @@
       </c>
       <c r="D53" s="2"/>
       <c r="E53" s="3"/>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F53" s="3"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" s="3" t="s">
         <v>80</v>
       </c>
@@ -1654,8 +1764,9 @@
       </c>
       <c r="D54" s="2"/>
       <c r="E54" s="3"/>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F54" s="3"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" s="3" t="s">
         <v>80</v>
       </c>
@@ -1667,8 +1778,9 @@
       </c>
       <c r="D55" s="2"/>
       <c r="E55" s="3"/>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F55" s="3"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" s="3" t="s">
         <v>80</v>
       </c>
@@ -1680,8 +1792,9 @@
       </c>
       <c r="D56" s="2"/>
       <c r="E56" s="3"/>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F56" s="3"/>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" s="3" t="s">
         <v>80</v>
       </c>
@@ -1693,8 +1806,9 @@
       </c>
       <c r="D57" s="2"/>
       <c r="E57" s="3"/>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F57" s="3"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" s="3" t="s">
         <v>80</v>
       </c>
@@ -1706,8 +1820,9 @@
       </c>
       <c r="D58" s="2"/>
       <c r="E58" s="3"/>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F58" s="3"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="3" t="s">
         <v>80</v>
       </c>
@@ -1719,8 +1834,9 @@
       </c>
       <c r="D59" s="2"/>
       <c r="E59" s="3"/>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F59" s="3"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="3" t="s">
         <v>80</v>
       </c>
@@ -1732,8 +1848,9 @@
       </c>
       <c r="D60" s="2"/>
       <c r="E60" s="3"/>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F60" s="3"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" s="3" t="s">
         <v>80</v>
       </c>
@@ -1745,8 +1862,9 @@
       </c>
       <c r="D61" s="2"/>
       <c r="E61" s="3"/>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F61" s="3"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" s="3" t="s">
         <v>80</v>
       </c>
@@ -1758,8 +1876,9 @@
       </c>
       <c r="D62" s="2"/>
       <c r="E62" s="3"/>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F62" s="3"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" s="3" t="s">
         <v>80</v>
       </c>
@@ -1771,8 +1890,9 @@
       </c>
       <c r="D63" s="2"/>
       <c r="E63" s="3"/>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F63" s="3"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" s="3" t="s">
         <v>80</v>
       </c>
@@ -1784,8 +1904,9 @@
       </c>
       <c r="D64" s="2"/>
       <c r="E64" s="3"/>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F64" s="3"/>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" s="3" t="s">
         <v>80</v>
       </c>
@@ -1797,8 +1918,9 @@
       </c>
       <c r="D65" s="2"/>
       <c r="E65" s="3"/>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F65" s="3"/>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" s="3" t="s">
         <v>80</v>
       </c>
@@ -1810,8 +1932,9 @@
       </c>
       <c r="D66" s="2"/>
       <c r="E66" s="3"/>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F66" s="3"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" s="3" t="s">
         <v>80</v>
       </c>
@@ -1823,8 +1946,9 @@
       </c>
       <c r="D67" s="2"/>
       <c r="E67" s="3"/>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F67" s="3"/>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" s="3" t="s">
         <v>80</v>
       </c>
@@ -1836,8 +1960,9 @@
       </c>
       <c r="D68" s="2"/>
       <c r="E68" s="3"/>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F68" s="3"/>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" s="3" t="s">
         <v>80</v>
       </c>
@@ -1849,8 +1974,9 @@
       </c>
       <c r="D69" s="2"/>
       <c r="E69" s="3"/>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F69" s="3"/>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" s="3" t="s">
         <v>80</v>
       </c>
@@ -1862,8 +1988,9 @@
       </c>
       <c r="D70" s="2"/>
       <c r="E70" s="3"/>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F70" s="3"/>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" s="3" t="s">
         <v>80</v>
       </c>
@@ -1875,8 +2002,9 @@
       </c>
       <c r="D71" s="2"/>
       <c r="E71" s="3"/>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F71" s="3"/>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" s="3" t="s">
         <v>80</v>
       </c>
@@ -1888,8 +2016,9 @@
       </c>
       <c r="D72" s="2"/>
       <c r="E72" s="3"/>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F72" s="3"/>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" s="3" t="s">
         <v>80</v>
       </c>
@@ -1901,8 +2030,9 @@
       </c>
       <c r="D73" s="2"/>
       <c r="E73" s="3"/>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F73" s="3"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" s="3" t="s">
         <v>80</v>
       </c>
@@ -1914,8 +2044,9 @@
       </c>
       <c r="D74" s="2"/>
       <c r="E74" s="3"/>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F74" s="3"/>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" s="3" t="s">
         <v>80</v>
       </c>
@@ -1927,8 +2058,9 @@
       </c>
       <c r="D75" s="2"/>
       <c r="E75" s="3"/>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F75" s="3"/>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" s="3" t="s">
         <v>80</v>
       </c>
@@ -1940,8 +2072,9 @@
       </c>
       <c r="D76" s="2"/>
       <c r="E76" s="3"/>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F76" s="3"/>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77" s="3" t="s">
         <v>80</v>
       </c>
@@ -1953,8 +2086,9 @@
       </c>
       <c r="D77" s="2"/>
       <c r="E77" s="3"/>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F77" s="3"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" s="3" t="s">
         <v>80</v>
       </c>
@@ -1966,8 +2100,9 @@
       </c>
       <c r="D78" s="2"/>
       <c r="E78" s="3"/>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F78" s="3"/>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79" s="3" t="s">
         <v>80</v>
       </c>
@@ -1979,8 +2114,9 @@
       </c>
       <c r="D79" s="2"/>
       <c r="E79" s="3"/>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F79" s="3"/>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>40</v>
       </c>
@@ -1994,8 +2130,9 @@
         <v>104</v>
       </c>
       <c r="E80" s="3"/>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F80" s="3"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>40</v>
       </c>
@@ -2011,8 +2148,9 @@
       <c r="E81" s="3" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F81" s="3"/>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>40</v>
       </c>
@@ -2026,8 +2164,9 @@
         <v>104</v>
       </c>
       <c r="E82" s="3"/>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F82" s="3"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>40</v>
       </c>
@@ -2043,8 +2182,9 @@
       <c r="E83" s="3" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F83" s="3"/>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>40</v>
       </c>
@@ -2060,8 +2200,9 @@
       <c r="E84" s="3" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F84" s="3"/>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>40</v>
       </c>
@@ -2072,13 +2213,14 @@
         <v>90</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F85" s="3"/>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>40</v>
       </c>
@@ -2089,13 +2231,14 @@
         <v>91</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E86" s="3" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F86" s="3"/>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>40</v>
       </c>
@@ -2109,8 +2252,9 @@
         <v>104</v>
       </c>
       <c r="E87" s="3"/>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F87" s="3"/>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>40</v>
       </c>
@@ -2124,8 +2268,9 @@
         <v>104</v>
       </c>
       <c r="E88" s="3"/>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F88" s="3"/>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>40</v>
       </c>
@@ -2136,11 +2281,12 @@
         <v>94</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E89" s="3"/>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F89" s="3"/>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>40</v>
       </c>
@@ -2154,8 +2300,9 @@
         <v>104</v>
       </c>
       <c r="E90" s="3"/>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F90" s="3"/>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>40</v>
       </c>
@@ -2166,11 +2313,12 @@
         <v>96</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="E91" s="3"/>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F91" s="3"/>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>40</v>
       </c>
@@ -2186,8 +2334,9 @@
       <c r="E92" s="3" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F92" s="3"/>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>40</v>
       </c>
@@ -2201,8 +2350,9 @@
         <v>104</v>
       </c>
       <c r="E93" s="3"/>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F93" s="3"/>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>40</v>
       </c>
@@ -2218,8 +2368,9 @@
       <c r="E94" s="3" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F94" s="3"/>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>40</v>
       </c>
@@ -2229,14 +2380,17 @@
       <c r="C95" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D95" s="2" t="s">
-        <v>85</v>
+      <c r="D95" s="7">
+        <v>100084810500176</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F95" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>40</v>
       </c>
@@ -2246,12 +2400,15 @@
       <c r="C96" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="D96" s="2" t="s">
+      <c r="D96" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="E96" s="3"/>
+      <c r="F96" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E96" s="3"/>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>40</v>
       </c>
@@ -2261,12 +2418,15 @@
       <c r="C97" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D97" s="2" t="s">
+      <c r="D97" s="7">
+        <v>100084810500176</v>
+      </c>
+      <c r="E97" s="3"/>
+      <c r="F97" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E97" s="3"/>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>40</v>
       </c>
@@ -2280,8 +2440,9 @@
         <v>104</v>
       </c>
       <c r="E98" s="3"/>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F98" s="3"/>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>40</v>
       </c>
@@ -2291,14 +2452,17 @@
       <c r="C99" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="D99" s="2" t="s">
-        <v>85</v>
+      <c r="D99" s="7">
+        <v>100084810500176</v>
       </c>
       <c r="E99" s="3" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F99" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>40</v>
       </c>
@@ -2314,8 +2478,9 @@
       <c r="E100" s="3" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F100" s="3"/>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>40</v>
       </c>
@@ -2329,8 +2494,9 @@
         <v>104</v>
       </c>
       <c r="E101" s="3"/>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F101" s="3"/>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>40</v>
       </c>
@@ -2344,8 +2510,9 @@
         <v>104</v>
       </c>
       <c r="E102" s="3"/>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F102" s="3"/>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>40</v>
       </c>
@@ -2359,8 +2526,9 @@
         <v>104</v>
       </c>
       <c r="E103" s="3"/>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F103" s="3"/>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>40</v>
       </c>
@@ -2374,8 +2542,9 @@
         <v>104</v>
       </c>
       <c r="E104" s="3"/>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F104" s="3"/>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>40</v>
       </c>
@@ -2385,14 +2554,17 @@
       <c r="C105" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="D105" s="2" t="s">
-        <v>85</v>
+      <c r="D105" s="7">
+        <v>100084810500176</v>
       </c>
       <c r="E105" s="3" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F105" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>40</v>
       </c>
@@ -2402,12 +2574,15 @@
       <c r="C106" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="D106" s="2" t="s">
+      <c r="D106" s="7">
+        <v>100084810500176</v>
+      </c>
+      <c r="E106" s="3"/>
+      <c r="F106" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E106" s="3"/>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>40</v>
       </c>
@@ -2417,12 +2592,15 @@
       <c r="C107" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D107" s="2" t="s">
+      <c r="D107" s="7">
+        <v>100084810500176</v>
+      </c>
+      <c r="E107" s="3"/>
+      <c r="F107" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E107" s="3"/>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>40</v>
       </c>
@@ -2433,11 +2611,14 @@
         <v>123</v>
       </c>
       <c r="D108" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E108" s="3"/>
+      <c r="F108" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E108" s="3"/>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>40</v>
       </c>
@@ -2447,12 +2628,15 @@
       <c r="C109" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="D109" s="2" t="s">
+      <c r="D109" s="7">
+        <v>100084810500176</v>
+      </c>
+      <c r="E109" s="3"/>
+      <c r="F109" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E109" s="3"/>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>40</v>
       </c>
@@ -2462,12 +2646,13 @@
       <c r="C110" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="D110" s="2" t="s">
-        <v>85</v>
+      <c r="D110" s="7">
+        <v>100084810500176</v>
       </c>
       <c r="E110" s="3"/>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F110" s="3"/>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>40</v>
       </c>
@@ -2477,12 +2662,13 @@
       <c r="C111" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="D111" s="2" t="s">
-        <v>85</v>
+      <c r="D111" s="7">
+        <v>100084810500176</v>
       </c>
       <c r="E111" s="3"/>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F111" s="3"/>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>40</v>
       </c>
@@ -2492,12 +2678,13 @@
       <c r="C112" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="D112" s="2" t="s">
-        <v>85</v>
+      <c r="D112" s="7">
+        <v>100084810500176</v>
       </c>
       <c r="E112" s="3"/>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F112" s="3"/>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>40</v>
       </c>
@@ -2507,12 +2694,13 @@
       <c r="C113" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="D113" s="2" t="s">
-        <v>85</v>
+      <c r="D113" s="7">
+        <v>100084810500176</v>
       </c>
       <c r="E113" s="3"/>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F113" s="3"/>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>40</v>
       </c>
@@ -2522,12 +2710,13 @@
       <c r="C114" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="D114" s="2" t="s">
-        <v>85</v>
+      <c r="D114" s="7">
+        <v>100084810500176</v>
       </c>
       <c r="E114" s="3"/>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F114" s="3"/>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>40</v>
       </c>
@@ -2537,12 +2726,13 @@
       <c r="C115" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="D115" s="2" t="s">
-        <v>85</v>
+      <c r="D115" s="7">
+        <v>100084810500176</v>
       </c>
       <c r="E115" s="3"/>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F115" s="3"/>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>40</v>
       </c>
@@ -2552,12 +2742,13 @@
       <c r="C116" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="D116" s="2" t="s">
-        <v>85</v>
+      <c r="D116" s="7">
+        <v>100084810500176</v>
       </c>
       <c r="E116" s="3"/>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F116" s="3"/>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>40</v>
       </c>
@@ -2567,12 +2758,13 @@
       <c r="C117" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="D117" s="2" t="s">
-        <v>85</v>
+      <c r="D117" s="7">
+        <v>100084810500176</v>
       </c>
       <c r="E117" s="3"/>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F117" s="3"/>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>40</v>
       </c>
@@ -2582,12 +2774,15 @@
       <c r="C118" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="D118" s="2" t="s">
+      <c r="D118" s="7">
+        <v>100084810500176</v>
+      </c>
+      <c r="E118" s="3"/>
+      <c r="F118" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E118" s="3"/>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>40</v>
       </c>
@@ -2601,8 +2796,11 @@
         <v>85</v>
       </c>
       <c r="E119" s="3"/>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F119" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>40</v>
       </c>
@@ -2616,8 +2814,11 @@
         <v>85</v>
       </c>
       <c r="E120" s="3"/>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F120" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>40</v>
       </c>
@@ -2631,8 +2832,11 @@
         <v>85</v>
       </c>
       <c r="E121" s="3"/>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F121" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>40</v>
       </c>
@@ -2646,6 +2850,179 @@
         <v>85</v>
       </c>
       <c r="E122" s="3"/>
+      <c r="F122" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A123" t="s">
+        <v>40</v>
+      </c>
+      <c r="B123" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="C123" t="s">
+        <v>130</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F123" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A124" t="s">
+        <v>40</v>
+      </c>
+      <c r="B124" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="C124" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F124" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A125" t="s">
+        <v>40</v>
+      </c>
+      <c r="B125" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="C125" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F125" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A126" t="s">
+        <v>40</v>
+      </c>
+      <c r="B126" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="C126" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F126" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A127" t="s">
+        <v>40</v>
+      </c>
+      <c r="B127" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="C127" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F127" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A128" t="s">
+        <v>40</v>
+      </c>
+      <c r="B128" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="C128" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F128" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A129" t="s">
+        <v>40</v>
+      </c>
+      <c r="B129" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="C129" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F129" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A130" t="s">
+        <v>40</v>
+      </c>
+      <c r="B130" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="C130" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F130" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A131" t="s">
+        <v>40</v>
+      </c>
+      <c r="B131" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="C131" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F131" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A132" t="s">
+        <v>40</v>
+      </c>
+      <c r="B132" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="C132" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F132" s="3" t="s">
+        <v>141</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -2770,8 +3147,31 @@
     <hyperlink ref="C111" r:id="rId119"/>
     <hyperlink ref="C112" r:id="rId120"/>
     <hyperlink ref="C113" r:id="rId121"/>
+    <hyperlink ref="F105" r:id="rId122"/>
+    <hyperlink ref="F106" r:id="rId123"/>
+    <hyperlink ref="F107" r:id="rId124"/>
+    <hyperlink ref="F99" r:id="rId125"/>
+    <hyperlink ref="F97" r:id="rId126"/>
+    <hyperlink ref="F96" r:id="rId127"/>
+    <hyperlink ref="F95" r:id="rId128"/>
+    <hyperlink ref="D85" r:id="rId129"/>
+    <hyperlink ref="D86" r:id="rId130"/>
+    <hyperlink ref="D89" r:id="rId131"/>
+    <hyperlink ref="D91" r:id="rId132" display="phuluuhoang16081993@gmail.com"/>
+    <hyperlink ref="D108" r:id="rId133"/>
+    <hyperlink ref="F108" r:id="rId134"/>
+    <hyperlink ref="F109" r:id="rId135"/>
+    <hyperlink ref="C124" r:id="rId136"/>
+    <hyperlink ref="C125" r:id="rId137"/>
+    <hyperlink ref="C126" r:id="rId138"/>
+    <hyperlink ref="C127" r:id="rId139"/>
+    <hyperlink ref="C128" r:id="rId140"/>
+    <hyperlink ref="C129" r:id="rId141"/>
+    <hyperlink ref="C130" r:id="rId142"/>
+    <hyperlink ref="C131" r:id="rId143"/>
+    <hyperlink ref="C132" r:id="rId144"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId122"/>
+  <pageSetup orientation="portrait" r:id="rId145"/>
 </worksheet>
 </file>